--- a/src/backend/data/hec_universities.xlsx
+++ b/src/backend/data/hec_universities.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sawera\uni-finder\src\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D546A0-A6BF-4112-8FAE-84161193D6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EBEE7B-F9E4-4B9A-8F0F-604054A876B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HEC Universities" sheetId="1" r:id="rId1"/>
@@ -235,9 +235,6 @@
     <t>University of Lahore</t>
   </si>
   <si>
-    <t>Haripur Campus; Karachi Campus; Peshawar Campus; Swabi Campus; Swat Campus; Wah Cantt Campus; Layyah Campus; Mianwali Campus; Sahiwal Campus; Sialkot Campus; Lahore (Main Campus); Sargodha Campus;</t>
-  </si>
-  <si>
     <t>@uol.edu.pk</t>
   </si>
   <si>
@@ -3887,6 +3884,9 @@
   </si>
   <si>
     <t>@gcu.edu.pk</t>
+  </si>
+  <si>
+    <t>Lahore (Main Campus);Lahore (City Campus); Sargodha Campus;Islamabad Campus; Pakpattan Campus; Gujrat Campus</t>
   </si>
 </sst>
 </file>
@@ -4688,30 +4688,30 @@
         <v>69</v>
       </c>
       <c r="C12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
         <v>70</v>
       </c>
-      <c r="D12">
-        <v>12</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>71</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>72</v>
-      </c>
-      <c r="H12" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
         <v>74</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
       </c>
       <c r="C13" t="s">
         <v>17</v>
@@ -4723,24 +4723,24 @@
         <v>18</v>
       </c>
       <c r="F13" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" t="s">
         <v>76</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>77</v>
-      </c>
-      <c r="H13" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
         <v>79</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>80</v>
-      </c>
-      <c r="C14" t="s">
-        <v>81</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -4749,24 +4749,24 @@
         <v>11</v>
       </c>
       <c r="F14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" t="s">
         <v>82</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>83</v>
-      </c>
-      <c r="H14" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
         <v>85</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>86</v>
-      </c>
-      <c r="C15" t="s">
-        <v>87</v>
       </c>
       <c r="D15">
         <v>10</v>
@@ -4775,47 +4775,47 @@
         <v>18</v>
       </c>
       <c r="F15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" t="s">
         <v>88</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>89</v>
-      </c>
-      <c r="H15" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
         <v>91</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>92</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
         <v>93</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>94</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>95</v>
-      </c>
-      <c r="H16" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" t="s">
         <v>97</v>
-      </c>
-      <c r="B17" t="s">
-        <v>98</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -4827,50 +4827,50 @@
         <v>11</v>
       </c>
       <c r="F17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" t="s">
         <v>99</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>100</v>
-      </c>
-      <c r="H17" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" t="s">
         <v>102</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>103</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
         <v>104</v>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>105</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>106</v>
-      </c>
-      <c r="H18" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
         <v>108</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>109</v>
-      </c>
-      <c r="C19" t="s">
-        <v>110</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -4879,50 +4879,50 @@
         <v>18</v>
       </c>
       <c r="F19" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" t="s">
         <v>111</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>112</v>
-      </c>
-      <c r="H19" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" t="s">
         <v>114</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>115</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
         <v>116</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>117</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>118</v>
-      </c>
-      <c r="H20" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" t="s">
         <v>120</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>121</v>
-      </c>
-      <c r="C21" t="s">
-        <v>122</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -4931,21 +4931,21 @@
         <v>11</v>
       </c>
       <c r="F21" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" t="s">
         <v>123</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>124</v>
-      </c>
-      <c r="H21" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" t="s">
         <v>126</v>
-      </c>
-      <c r="B22" t="s">
-        <v>127</v>
       </c>
       <c r="C22" t="s">
         <v>58</v>
@@ -4957,21 +4957,21 @@
         <v>11</v>
       </c>
       <c r="F22" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" t="s">
         <v>128</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>129</v>
-      </c>
-      <c r="H22" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
         <v>131</v>
-      </c>
-      <c r="B23" t="s">
-        <v>132</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -4983,24 +4983,24 @@
         <v>11</v>
       </c>
       <c r="F23" t="s">
+        <v>132</v>
+      </c>
+      <c r="G23" t="s">
         <v>133</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>134</v>
-      </c>
-      <c r="H23" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" t="s">
         <v>136</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>137</v>
-      </c>
-      <c r="C24" t="s">
-        <v>138</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -5009,24 +5009,24 @@
         <v>11</v>
       </c>
       <c r="F24" t="s">
+        <v>138</v>
+      </c>
+      <c r="G24" t="s">
         <v>139</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>140</v>
-      </c>
-      <c r="H24" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" t="s">
         <v>142</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>143</v>
-      </c>
-      <c r="C25" t="s">
-        <v>144</v>
       </c>
       <c r="D25">
         <v>4</v>
@@ -5036,18 +5036,18 @@
       </c>
       <c r="F25" s="6"/>
       <c r="G25" t="s">
+        <v>144</v>
+      </c>
+      <c r="H25" t="s">
         <v>145</v>
-      </c>
-      <c r="H25" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" t="s">
         <v>147</v>
-      </c>
-      <c r="B26" t="s">
-        <v>148</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
@@ -5059,21 +5059,21 @@
         <v>11</v>
       </c>
       <c r="F26" t="s">
+        <v>148</v>
+      </c>
+      <c r="G26" t="s">
         <v>149</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>150</v>
-      </c>
-      <c r="H26" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" t="s">
         <v>152</v>
-      </c>
-      <c r="B27" t="s">
-        <v>153</v>
       </c>
       <c r="C27" t="s">
         <v>17</v>
@@ -5085,47 +5085,47 @@
         <v>11</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="G27" t="s">
+        <v>153</v>
+      </c>
+      <c r="H27" s="7" t="s">
         <v>154</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" t="s">
         <v>156</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
         <v>157</v>
       </c>
-      <c r="C28" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>158</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>159</v>
-      </c>
-      <c r="H28" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" t="s">
         <v>161</v>
-      </c>
-      <c r="B29" t="s">
-        <v>162</v>
       </c>
       <c r="C29" t="s">
         <v>58</v>
@@ -5137,21 +5137,21 @@
         <v>11</v>
       </c>
       <c r="F29" t="s">
+        <v>162</v>
+      </c>
+      <c r="G29" t="s">
         <v>163</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>164</v>
-      </c>
-      <c r="H29" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
+        <v>165</v>
+      </c>
+      <c r="B30" t="s">
         <v>166</v>
-      </c>
-      <c r="B30" t="s">
-        <v>167</v>
       </c>
       <c r="C30" t="s">
         <v>17</v>
@@ -5163,13 +5163,13 @@
         <v>18</v>
       </c>
       <c r="F30" t="s">
+        <v>167</v>
+      </c>
+      <c r="G30" t="s">
         <v>168</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>169</v>
-      </c>
-      <c r="H30" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -5177,7 +5177,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C31" t="s">
         <v>58</v>
@@ -5189,21 +5189,21 @@
         <v>18</v>
       </c>
       <c r="F31" t="s">
+        <v>171</v>
+      </c>
+      <c r="G31" t="s">
         <v>172</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>173</v>
-      </c>
-      <c r="H31" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
+        <v>174</v>
+      </c>
+      <c r="B32" t="s">
         <v>175</v>
-      </c>
-      <c r="B32" t="s">
-        <v>176</v>
       </c>
       <c r="C32" t="s">
         <v>58</v>
@@ -5215,24 +5215,24 @@
         <v>18</v>
       </c>
       <c r="F32" t="s">
+        <v>176</v>
+      </c>
+      <c r="G32" t="s">
         <v>177</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>178</v>
-      </c>
-      <c r="H32" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" t="s">
         <v>180</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>181</v>
-      </c>
-      <c r="C33" t="s">
-        <v>182</v>
       </c>
       <c r="D33">
         <v>10</v>
@@ -5241,21 +5241,21 @@
         <v>11</v>
       </c>
       <c r="F33" t="s">
+        <v>182</v>
+      </c>
+      <c r="G33" t="s">
         <v>183</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>184</v>
-      </c>
-      <c r="H33" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" t="s">
         <v>186</v>
-      </c>
-      <c r="B34" t="s">
-        <v>187</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
@@ -5267,50 +5267,50 @@
         <v>11</v>
       </c>
       <c r="F34" t="s">
+        <v>187</v>
+      </c>
+      <c r="G34" t="s">
         <v>188</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>189</v>
-      </c>
-      <c r="H34" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" t="s">
         <v>191</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" t="s">
         <v>192</v>
       </c>
-      <c r="C35" t="s">
-        <v>104</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>193</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>194</v>
-      </c>
-      <c r="H35" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" t="s">
         <v>196</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>197</v>
-      </c>
-      <c r="C36" t="s">
-        <v>198</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -5319,24 +5319,24 @@
         <v>18</v>
       </c>
       <c r="F36" t="s">
+        <v>198</v>
+      </c>
+      <c r="G36" t="s">
         <v>199</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>200</v>
-      </c>
-      <c r="H36" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
+        <v>201</v>
+      </c>
+      <c r="B37" t="s">
         <v>202</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>203</v>
-      </c>
-      <c r="C37" t="s">
-        <v>204</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -5345,24 +5345,24 @@
         <v>11</v>
       </c>
       <c r="F37" t="s">
+        <v>204</v>
+      </c>
+      <c r="G37" t="s">
         <v>205</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>206</v>
-      </c>
-      <c r="H37" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" t="s">
         <v>208</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>209</v>
-      </c>
-      <c r="C38" t="s">
-        <v>210</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -5371,24 +5371,24 @@
         <v>11</v>
       </c>
       <c r="F38" t="s">
+        <v>210</v>
+      </c>
+      <c r="G38" t="s">
         <v>211</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>212</v>
-      </c>
-      <c r="H38" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
+        <v>213</v>
+      </c>
+      <c r="B39" t="s">
         <v>214</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>215</v>
-      </c>
-      <c r="C39" t="s">
-        <v>216</v>
       </c>
       <c r="D39">
         <v>10</v>
@@ -5397,24 +5397,24 @@
         <v>11</v>
       </c>
       <c r="F39" t="s">
+        <v>216</v>
+      </c>
+      <c r="G39" t="s">
         <v>217</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>218</v>
-      </c>
-      <c r="H39" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
+        <v>219</v>
+      </c>
+      <c r="B40" t="s">
         <v>220</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>221</v>
-      </c>
-      <c r="C40" t="s">
-        <v>222</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -5423,21 +5423,21 @@
         <v>11</v>
       </c>
       <c r="F40" t="s">
+        <v>222</v>
+      </c>
+      <c r="G40" t="s">
         <v>223</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>224</v>
-      </c>
-      <c r="H40" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
+        <v>225</v>
+      </c>
+      <c r="B41" t="s">
         <v>226</v>
-      </c>
-      <c r="B41" t="s">
-        <v>227</v>
       </c>
       <c r="C41" t="s">
         <v>58</v>
@@ -5449,50 +5449,50 @@
         <v>11</v>
       </c>
       <c r="F41" t="s">
+        <v>227</v>
+      </c>
+      <c r="G41" t="s">
         <v>228</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>229</v>
-      </c>
-      <c r="H41" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
+        <v>230</v>
+      </c>
+      <c r="B42" t="s">
         <v>231</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>232</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" t="s">
         <v>233</v>
       </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>234</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>235</v>
-      </c>
-      <c r="H42" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
+        <v>236</v>
+      </c>
+      <c r="B43" t="s">
         <v>237</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>238</v>
-      </c>
-      <c r="C43" t="s">
-        <v>239</v>
       </c>
       <c r="D43">
         <v>7</v>
@@ -5501,21 +5501,21 @@
         <v>11</v>
       </c>
       <c r="F43" t="s">
+        <v>239</v>
+      </c>
+      <c r="G43" t="s">
         <v>240</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>241</v>
-      </c>
-      <c r="H43" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
+        <v>242</v>
+      </c>
+      <c r="B44" t="s">
         <v>243</v>
-      </c>
-      <c r="B44" t="s">
-        <v>244</v>
       </c>
       <c r="C44" t="s">
         <v>10</v>
@@ -5527,21 +5527,21 @@
         <v>18</v>
       </c>
       <c r="F44" t="s">
+        <v>244</v>
+      </c>
+      <c r="G44" t="s">
         <v>245</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>246</v>
-      </c>
-      <c r="H44" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
+        <v>247</v>
+      </c>
+      <c r="B45" t="s">
         <v>248</v>
-      </c>
-      <c r="B45" t="s">
-        <v>249</v>
       </c>
       <c r="C45" t="s">
         <v>58</v>
@@ -5553,47 +5553,47 @@
         <v>18</v>
       </c>
       <c r="F45" t="s">
+        <v>249</v>
+      </c>
+      <c r="G45" t="s">
         <v>250</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>251</v>
-      </c>
-      <c r="H45" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
+        <v>252</v>
+      </c>
+      <c r="B46" t="s">
         <v>253</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>254</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" t="s">
         <v>255</v>
       </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>256</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>257</v>
-      </c>
-      <c r="H46" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
+        <v>258</v>
+      </c>
+      <c r="B47" t="s">
         <v>259</v>
-      </c>
-      <c r="B47" t="s">
-        <v>260</v>
       </c>
       <c r="C47" t="s">
         <v>58</v>
@@ -5606,47 +5606,47 @@
       </c>
       <c r="F47" s="6"/>
       <c r="G47" t="s">
+        <v>260</v>
+      </c>
+      <c r="H47" t="s">
         <v>261</v>
-      </c>
-      <c r="H47" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
+        <v>262</v>
+      </c>
+      <c r="B48" t="s">
         <v>263</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>264</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" t="s">
         <v>265</v>
       </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>266</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>267</v>
-      </c>
-      <c r="H48" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
+        <v>268</v>
+      </c>
+      <c r="B49" t="s">
         <v>269</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>270</v>
-      </c>
-      <c r="C49" t="s">
-        <v>271</v>
       </c>
       <c r="D49">
         <v>5</v>
@@ -5655,73 +5655,73 @@
         <v>18</v>
       </c>
       <c r="F49" t="s">
+        <v>271</v>
+      </c>
+      <c r="G49" t="s">
         <v>272</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>273</v>
-      </c>
-      <c r="H49" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
+        <v>274</v>
+      </c>
+      <c r="B50" t="s">
         <v>275</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>276</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" t="s">
         <v>277</v>
       </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>278</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>279</v>
-      </c>
-      <c r="H50" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
+        <v>280</v>
+      </c>
+      <c r="B51" t="s">
         <v>281</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
+        <v>254</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" t="s">
         <v>282</v>
       </c>
-      <c r="C51" t="s">
-        <v>255</v>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>283</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>284</v>
-      </c>
-      <c r="H51" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
+        <v>285</v>
+      </c>
+      <c r="B52" t="s">
         <v>286</v>
-      </c>
-      <c r="B52" t="s">
-        <v>287</v>
       </c>
       <c r="C52" t="s">
         <v>10</v>
@@ -5733,21 +5733,21 @@
         <v>11</v>
       </c>
       <c r="F52" t="s">
+        <v>287</v>
+      </c>
+      <c r="G52" t="s">
         <v>288</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>289</v>
-      </c>
-      <c r="H52" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
+        <v>290</v>
+      </c>
+      <c r="B53" t="s">
         <v>291</v>
-      </c>
-      <c r="B53" t="s">
-        <v>292</v>
       </c>
       <c r="C53" t="s">
         <v>17</v>
@@ -5760,44 +5760,44 @@
       </c>
       <c r="F53" s="6"/>
       <c r="G53" t="s">
+        <v>292</v>
+      </c>
+      <c r="H53" t="s">
         <v>293</v>
-      </c>
-      <c r="H53" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
+        <v>294</v>
+      </c>
+      <c r="B54" t="s">
         <v>295</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>296</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" t="s">
         <v>297</v>
       </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>298</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>299</v>
-      </c>
-      <c r="H54" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
+        <v>300</v>
+      </c>
+      <c r="B55" t="s">
         <v>301</v>
-      </c>
-      <c r="B55" t="s">
-        <v>302</v>
       </c>
       <c r="C55" t="s">
         <v>17</v>
@@ -5810,18 +5810,18 @@
       </c>
       <c r="F55" s="6"/>
       <c r="G55" t="s">
+        <v>302</v>
+      </c>
+      <c r="H55" t="s">
         <v>303</v>
-      </c>
-      <c r="H55" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
+        <v>304</v>
+      </c>
+      <c r="B56" t="s">
         <v>305</v>
-      </c>
-      <c r="B56" t="s">
-        <v>306</v>
       </c>
       <c r="C56" t="s">
         <v>58</v>
@@ -5833,24 +5833,24 @@
         <v>18</v>
       </c>
       <c r="F56" t="s">
+        <v>306</v>
+      </c>
+      <c r="G56" t="s">
         <v>307</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>308</v>
-      </c>
-      <c r="H56" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
+        <v>309</v>
+      </c>
+      <c r="B57" t="s">
         <v>310</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>311</v>
-      </c>
-      <c r="C57" t="s">
-        <v>312</v>
       </c>
       <c r="D57">
         <v>4</v>
@@ -5859,24 +5859,24 @@
         <v>11</v>
       </c>
       <c r="F57" t="s">
+        <v>312</v>
+      </c>
+      <c r="G57" t="s">
         <v>313</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>314</v>
-      </c>
-      <c r="H57" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
+        <v>315</v>
+      </c>
+      <c r="B58" t="s">
         <v>316</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>317</v>
-      </c>
-      <c r="C58" t="s">
-        <v>318</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -5885,24 +5885,24 @@
         <v>11</v>
       </c>
       <c r="F58" t="s">
+        <v>318</v>
+      </c>
+      <c r="G58" t="s">
         <v>319</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>320</v>
-      </c>
-      <c r="H58" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
+        <v>321</v>
+      </c>
+      <c r="B59" t="s">
         <v>322</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>323</v>
-      </c>
-      <c r="C59" t="s">
-        <v>324</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -5912,21 +5912,21 @@
       </c>
       <c r="F59" s="6"/>
       <c r="G59" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
+        <v>325</v>
+      </c>
+      <c r="B60" t="s">
         <v>326</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>327</v>
-      </c>
-      <c r="C60" t="s">
-        <v>328</v>
       </c>
       <c r="D60">
         <v>4</v>
@@ -5935,21 +5935,21 @@
         <v>11</v>
       </c>
       <c r="F60" t="s">
+        <v>328</v>
+      </c>
+      <c r="G60" t="s">
         <v>329</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>330</v>
-      </c>
-      <c r="H60" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
+        <v>331</v>
+      </c>
+      <c r="B61" t="s">
         <v>332</v>
-      </c>
-      <c r="B61" t="s">
-        <v>333</v>
       </c>
       <c r="C61" t="s">
         <v>10</v>
@@ -5962,18 +5962,18 @@
       </c>
       <c r="F61" s="6"/>
       <c r="G61" t="s">
+        <v>333</v>
+      </c>
+      <c r="H61" t="s">
         <v>334</v>
-      </c>
-      <c r="H61" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
+        <v>335</v>
+      </c>
+      <c r="B62" t="s">
         <v>336</v>
-      </c>
-      <c r="B62" t="s">
-        <v>337</v>
       </c>
       <c r="C62" t="s">
         <v>58</v>
@@ -5986,47 +5986,47 @@
       </c>
       <c r="F62"/>
       <c r="G62" t="s">
+        <v>337</v>
+      </c>
+      <c r="H62" t="s">
         <v>338</v>
-      </c>
-      <c r="H62" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
+        <v>339</v>
+      </c>
+      <c r="B63" t="s">
         <v>340</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>341</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" t="s">
         <v>342</v>
       </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>343</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>344</v>
-      </c>
-      <c r="H63" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
+        <v>345</v>
+      </c>
+      <c r="B64" t="s">
         <v>346</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>347</v>
-      </c>
-      <c r="C64" t="s">
-        <v>348</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -6036,44 +6036,44 @@
       </c>
       <c r="F64" s="6"/>
       <c r="G64" t="s">
+        <v>348</v>
+      </c>
+      <c r="H64" t="s">
         <v>349</v>
-      </c>
-      <c r="H64" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
+        <v>350</v>
+      </c>
+      <c r="B65" t="s">
         <v>351</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
+        <v>254</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" t="s">
         <v>352</v>
       </c>
-      <c r="C65" t="s">
-        <v>255</v>
-      </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>353</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>354</v>
-      </c>
-      <c r="H65" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
+        <v>355</v>
+      </c>
+      <c r="B66" t="s">
         <v>356</v>
-      </c>
-      <c r="B66" t="s">
-        <v>357</v>
       </c>
       <c r="C66" t="s">
         <v>58</v>
@@ -6085,21 +6085,21 @@
         <v>18</v>
       </c>
       <c r="F66" t="s">
+        <v>357</v>
+      </c>
+      <c r="G66" t="s">
         <v>358</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>359</v>
-      </c>
-      <c r="H66" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
+        <v>360</v>
+      </c>
+      <c r="B67" t="s">
         <v>361</v>
-      </c>
-      <c r="B67" t="s">
-        <v>362</v>
       </c>
       <c r="C67" t="s">
         <v>17</v>
@@ -6111,24 +6111,24 @@
         <v>11</v>
       </c>
       <c r="F67" t="s">
+        <v>362</v>
+      </c>
+      <c r="G67" t="s">
         <v>363</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>364</v>
-      </c>
-      <c r="H67" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
+        <v>365</v>
+      </c>
+      <c r="B68" t="s">
         <v>366</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>367</v>
-      </c>
-      <c r="C68" t="s">
-        <v>368</v>
       </c>
       <c r="D68">
         <v>3</v>
@@ -6137,21 +6137,21 @@
         <v>11</v>
       </c>
       <c r="F68" t="s">
+        <v>368</v>
+      </c>
+      <c r="G68" t="s">
         <v>369</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>370</v>
-      </c>
-      <c r="H68" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
+        <v>371</v>
+      </c>
+      <c r="B69" t="s">
         <v>372</v>
-      </c>
-      <c r="B69" t="s">
-        <v>373</v>
       </c>
       <c r="C69" t="s">
         <v>10</v>
@@ -6163,21 +6163,21 @@
         <v>11</v>
       </c>
       <c r="F69" t="s">
+        <v>373</v>
+      </c>
+      <c r="G69" t="s">
         <v>374</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>375</v>
-      </c>
-      <c r="H69" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
+        <v>376</v>
+      </c>
+      <c r="B70" t="s">
         <v>377</v>
-      </c>
-      <c r="B70" t="s">
-        <v>378</v>
       </c>
       <c r="C70" t="s">
         <v>10</v>
@@ -6189,47 +6189,47 @@
         <v>18</v>
       </c>
       <c r="F70" t="s">
+        <v>378</v>
+      </c>
+      <c r="G70" t="s">
         <v>379</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>380</v>
-      </c>
-      <c r="H70" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
+        <v>381</v>
+      </c>
+      <c r="B71" t="s">
         <v>382</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>383</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" t="s">
         <v>384</v>
       </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>385</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>386</v>
-      </c>
-      <c r="H71" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
+        <v>387</v>
+      </c>
+      <c r="B72" t="s">
         <v>388</v>
-      </c>
-      <c r="B72" t="s">
-        <v>389</v>
       </c>
       <c r="C72" t="s">
         <v>17</v>
@@ -6241,24 +6241,24 @@
         <v>18</v>
       </c>
       <c r="F72" t="s">
+        <v>389</v>
+      </c>
+      <c r="G72" t="s">
         <v>390</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>391</v>
-      </c>
-      <c r="H72" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
+        <v>392</v>
+      </c>
+      <c r="B73" t="s">
         <v>393</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>394</v>
-      </c>
-      <c r="C73" t="s">
-        <v>395</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -6268,21 +6268,21 @@
       </c>
       <c r="F73" s="6"/>
       <c r="G73" t="s">
+        <v>395</v>
+      </c>
+      <c r="H73" t="s">
         <v>396</v>
-      </c>
-      <c r="H73" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
+        <v>397</v>
+      </c>
+      <c r="B74" t="s">
         <v>398</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>399</v>
-      </c>
-      <c r="C74" t="s">
-        <v>400</v>
       </c>
       <c r="D74">
         <v>3</v>
@@ -6291,21 +6291,21 @@
         <v>18</v>
       </c>
       <c r="F74" t="s">
+        <v>400</v>
+      </c>
+      <c r="G74" t="s">
         <v>401</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>402</v>
-      </c>
-      <c r="H74" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
+        <v>403</v>
+      </c>
+      <c r="B75" t="s">
         <v>404</v>
-      </c>
-      <c r="B75" t="s">
-        <v>405</v>
       </c>
       <c r="C75" t="s">
         <v>17</v>
@@ -6318,73 +6318,73 @@
       </c>
       <c r="F75" s="6"/>
       <c r="G75" t="s">
+        <v>405</v>
+      </c>
+      <c r="H75" t="s">
         <v>406</v>
-      </c>
-      <c r="H75" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
+        <v>407</v>
+      </c>
+      <c r="B76" t="s">
         <v>408</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
+        <v>296</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" t="s">
         <v>409</v>
       </c>
-      <c r="C76" t="s">
-        <v>297</v>
-      </c>
-      <c r="D76">
-        <v>1</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>410</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>411</v>
-      </c>
-      <c r="H76" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
+        <v>412</v>
+      </c>
+      <c r="B77" t="s">
         <v>413</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>414</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" t="s">
         <v>415</v>
       </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>416</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>417</v>
-      </c>
-      <c r="H77" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
+        <v>418</v>
+      </c>
+      <c r="B78" t="s">
         <v>419</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>420</v>
-      </c>
-      <c r="C78" t="s">
-        <v>421</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -6394,21 +6394,21 @@
       </c>
       <c r="F78" s="6"/>
       <c r="G78" t="s">
+        <v>421</v>
+      </c>
+      <c r="H78" t="s">
         <v>422</v>
-      </c>
-      <c r="H78" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
+        <v>423</v>
+      </c>
+      <c r="B79" t="s">
         <v>424</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>425</v>
-      </c>
-      <c r="C79" t="s">
-        <v>426</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -6418,18 +6418,18 @@
       </c>
       <c r="F79" s="6"/>
       <c r="G79" t="s">
+        <v>426</v>
+      </c>
+      <c r="H79" t="s">
         <v>427</v>
-      </c>
-      <c r="H79" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
+        <v>428</v>
+      </c>
+      <c r="B80" t="s">
         <v>429</v>
-      </c>
-      <c r="B80" t="s">
-        <v>430</v>
       </c>
       <c r="C80" t="s">
         <v>58</v>
@@ -6441,21 +6441,21 @@
         <v>18</v>
       </c>
       <c r="F80" t="s">
+        <v>430</v>
+      </c>
+      <c r="G80" t="s">
         <v>431</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>432</v>
-      </c>
-      <c r="H80" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
+        <v>433</v>
+      </c>
+      <c r="B81" t="s">
         <v>434</v>
-      </c>
-      <c r="B81" t="s">
-        <v>435</v>
       </c>
       <c r="C81" t="s">
         <v>10</v>
@@ -6467,50 +6467,50 @@
         <v>18</v>
       </c>
       <c r="F81" t="s">
+        <v>435</v>
+      </c>
+      <c r="G81" t="s">
         <v>436</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>437</v>
-      </c>
-      <c r="H81" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
+        <v>438</v>
+      </c>
+      <c r="B82" t="s">
         <v>439</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
+        <v>92</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" t="s">
         <v>440</v>
       </c>
-      <c r="C82" t="s">
-        <v>93</v>
-      </c>
-      <c r="D82">
-        <v>1</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>441</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>442</v>
-      </c>
-      <c r="H82" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
+        <v>443</v>
+      </c>
+      <c r="B83" t="s">
         <v>444</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>445</v>
-      </c>
-      <c r="C83" t="s">
-        <v>446</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -6519,21 +6519,21 @@
         <v>18</v>
       </c>
       <c r="F83" t="s">
+        <v>446</v>
+      </c>
+      <c r="G83" t="s">
         <v>447</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>448</v>
-      </c>
-      <c r="H83" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" t="s">
+        <v>449</v>
+      </c>
+      <c r="B84" t="s">
         <v>450</v>
-      </c>
-      <c r="B84" t="s">
-        <v>451</v>
       </c>
       <c r="C84" t="s">
         <v>58</v>
@@ -6545,21 +6545,21 @@
         <v>18</v>
       </c>
       <c r="F84" t="s">
+        <v>451</v>
+      </c>
+      <c r="G84" t="s">
         <v>452</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>453</v>
-      </c>
-      <c r="H84" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
+        <v>454</v>
+      </c>
+      <c r="B85" t="s">
         <v>455</v>
-      </c>
-      <c r="B85" t="s">
-        <v>456</v>
       </c>
       <c r="C85" t="s">
         <v>58</v>
@@ -6571,24 +6571,24 @@
         <v>11</v>
       </c>
       <c r="F85" t="s">
+        <v>456</v>
+      </c>
+      <c r="G85" t="s">
         <v>457</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>458</v>
-      </c>
-      <c r="H85" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
+        <v>459</v>
+      </c>
+      <c r="B86" t="s">
         <v>460</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>461</v>
-      </c>
-      <c r="C86" t="s">
-        <v>462</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -6597,24 +6597,24 @@
         <v>18</v>
       </c>
       <c r="F86" t="s">
+        <v>462</v>
+      </c>
+      <c r="G86" t="s">
         <v>463</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>464</v>
-      </c>
-      <c r="H86" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
+        <v>465</v>
+      </c>
+      <c r="B87" t="s">
         <v>466</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>467</v>
-      </c>
-      <c r="C87" t="s">
-        <v>468</v>
       </c>
       <c r="D87">
         <v>2</v>
@@ -6624,18 +6624,18 @@
       </c>
       <c r="F87" s="6"/>
       <c r="G87" t="s">
+        <v>468</v>
+      </c>
+      <c r="H87" t="s">
         <v>469</v>
-      </c>
-      <c r="H87" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
+        <v>470</v>
+      </c>
+      <c r="B88" t="s">
         <v>471</v>
-      </c>
-      <c r="B88" t="s">
-        <v>472</v>
       </c>
       <c r="C88" t="s">
         <v>58</v>
@@ -6648,18 +6648,18 @@
       </c>
       <c r="F88" s="6"/>
       <c r="G88" t="s">
+        <v>472</v>
+      </c>
+      <c r="H88" t="s">
         <v>473</v>
-      </c>
-      <c r="H88" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
+        <v>474</v>
+      </c>
+      <c r="B89" t="s">
         <v>475</v>
-      </c>
-      <c r="B89" t="s">
-        <v>476</v>
       </c>
       <c r="C89" t="s">
         <v>17</v>
@@ -6671,21 +6671,21 @@
         <v>18</v>
       </c>
       <c r="F89" t="s">
+        <v>476</v>
+      </c>
+      <c r="G89" t="s">
         <v>477</v>
       </c>
-      <c r="G89" t="s">
+      <c r="H89" t="s">
         <v>478</v>
-      </c>
-      <c r="H89" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
+        <v>479</v>
+      </c>
+      <c r="B90" t="s">
         <v>480</v>
-      </c>
-      <c r="B90" t="s">
-        <v>481</v>
       </c>
       <c r="C90" t="s">
         <v>17</v>
@@ -6697,21 +6697,21 @@
         <v>11</v>
       </c>
       <c r="F90" t="s">
+        <v>481</v>
+      </c>
+      <c r="G90" t="s">
         <v>482</v>
       </c>
-      <c r="G90" t="s">
+      <c r="H90" t="s">
         <v>483</v>
-      </c>
-      <c r="H90" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" t="s">
+        <v>484</v>
+      </c>
+      <c r="B91" t="s">
         <v>485</v>
-      </c>
-      <c r="B91" t="s">
-        <v>486</v>
       </c>
       <c r="C91" t="s">
         <v>17</v>
@@ -6724,36 +6724,36 @@
       </c>
       <c r="F91" s="6"/>
       <c r="G91" t="s">
+        <v>486</v>
+      </c>
+      <c r="H91" t="s">
         <v>487</v>
-      </c>
-      <c r="H91" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" t="s">
+        <v>488</v>
+      </c>
+      <c r="B92" t="s">
         <v>489</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>490</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" t="s">
         <v>491</v>
       </c>
-      <c r="D92">
-        <v>1</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>492</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
         <v>493</v>
-      </c>
-      <c r="H92" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="93" spans="1:8" s="3" customFormat="1">
@@ -6761,10 +6761,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D93" s="3">
         <v>1</v>
@@ -6773,50 +6773,50 @@
         <v>11</v>
       </c>
       <c r="F93" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="G93" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="G93" s="3" t="s">
+      <c r="H93" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
+        <v>497</v>
+      </c>
+      <c r="B94" t="s">
         <v>498</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
+        <v>383</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" t="s">
         <v>499</v>
       </c>
-      <c r="C94" t="s">
-        <v>384</v>
-      </c>
-      <c r="D94">
-        <v>1</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>500</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>501</v>
-      </c>
-      <c r="H94" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
+        <v>502</v>
+      </c>
+      <c r="B95" t="s">
         <v>503</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
         <v>504</v>
-      </c>
-      <c r="C95" t="s">
-        <v>505</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -6826,44 +6826,44 @@
       </c>
       <c r="F95" s="6"/>
       <c r="G95" t="s">
+        <v>505</v>
+      </c>
+      <c r="H95" t="s">
         <v>506</v>
-      </c>
-      <c r="H95" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
+        <v>507</v>
+      </c>
+      <c r="B96" t="s">
         <v>508</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
         <v>509</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" t="s">
         <v>510</v>
       </c>
-      <c r="D96">
-        <v>1</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>511</v>
       </c>
-      <c r="G96" t="s">
+      <c r="H96" t="s">
         <v>512</v>
-      </c>
-      <c r="H96" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
+        <v>513</v>
+      </c>
+      <c r="B97" t="s">
         <v>514</v>
-      </c>
-      <c r="B97" t="s">
-        <v>515</v>
       </c>
       <c r="C97" t="s">
         <v>58</v>
@@ -6875,39 +6875,39 @@
         <v>18</v>
       </c>
       <c r="F97" t="s">
+        <v>515</v>
+      </c>
+      <c r="G97" t="s">
         <v>516</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>517</v>
-      </c>
-      <c r="H97" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
+        <v>518</v>
+      </c>
+      <c r="B98" t="s">
         <v>519</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>520</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F98" t="s">
         <v>521</v>
       </c>
-      <c r="D98">
-        <v>1</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>522</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
         <v>523</v>
-      </c>
-      <c r="H98" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="99" spans="1:8" s="3" customFormat="1">
@@ -6915,36 +6915,36 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="D99" s="3">
+        <v>1</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="D99" s="3">
-        <v>1</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F99" s="3" t="s">
+      <c r="G99" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="G99" s="3" t="s">
+      <c r="H99" s="3" t="s">
         <v>528</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
+        <v>529</v>
+      </c>
+      <c r="B100" t="s">
         <v>530</v>
       </c>
-      <c r="B100" t="s">
-        <v>531</v>
-      </c>
       <c r="C100" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -6954,47 +6954,47 @@
       </c>
       <c r="F100" s="6"/>
       <c r="G100" t="s">
+        <v>531</v>
+      </c>
+      <c r="H100" t="s">
         <v>532</v>
-      </c>
-      <c r="H100" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
+        <v>533</v>
+      </c>
+      <c r="B101" t="s">
         <v>534</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
+        <v>254</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" t="s">
         <v>535</v>
       </c>
-      <c r="C101" t="s">
-        <v>255</v>
-      </c>
-      <c r="D101">
-        <v>1</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>536</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>537</v>
-      </c>
-      <c r="H101" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
+        <v>538</v>
+      </c>
+      <c r="B102" t="s">
         <v>539</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>540</v>
-      </c>
-      <c r="C102" t="s">
-        <v>541</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -7003,47 +7003,47 @@
         <v>18</v>
       </c>
       <c r="F102" t="s">
+        <v>541</v>
+      </c>
+      <c r="G102" t="s">
         <v>542</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102" t="s">
         <v>543</v>
-      </c>
-      <c r="H102" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
+        <v>544</v>
+      </c>
+      <c r="B103" t="s">
         <v>545</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
         <v>546</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" t="s">
         <v>547</v>
       </c>
-      <c r="D103">
-        <v>1</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" t="s">
+      <c r="G103" t="s">
         <v>548</v>
       </c>
-      <c r="G103" t="s">
+      <c r="H103" t="s">
         <v>549</v>
-      </c>
-      <c r="H103" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" t="s">
+        <v>550</v>
+      </c>
+      <c r="B104" t="s">
         <v>551</v>
-      </c>
-      <c r="B104" t="s">
-        <v>552</v>
       </c>
       <c r="C104" t="s">
         <v>58</v>
@@ -7055,47 +7055,47 @@
         <v>18</v>
       </c>
       <c r="F104" t="s">
+        <v>552</v>
+      </c>
+      <c r="G104" t="s">
         <v>553</v>
       </c>
-      <c r="G104" t="s">
+      <c r="H104" t="s">
         <v>554</v>
-      </c>
-      <c r="H104" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" t="s">
+        <v>555</v>
+      </c>
+      <c r="B105" t="s">
         <v>556</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>557</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F105" t="s">
         <v>558</v>
       </c>
-      <c r="D105">
-        <v>1</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
         <v>559</v>
       </c>
-      <c r="G105" t="s">
+      <c r="H105" t="s">
         <v>560</v>
-      </c>
-      <c r="H105" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" t="s">
+        <v>561</v>
+      </c>
+      <c r="B106" t="s">
         <v>562</v>
-      </c>
-      <c r="B106" t="s">
-        <v>563</v>
       </c>
       <c r="C106" t="s">
         <v>58</v>
@@ -7108,73 +7108,73 @@
       </c>
       <c r="F106" s="6"/>
       <c r="G106" t="s">
+        <v>563</v>
+      </c>
+      <c r="H106" t="s">
         <v>564</v>
-      </c>
-      <c r="H106" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" t="s">
+        <v>565</v>
+      </c>
+      <c r="B107" t="s">
         <v>566</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
+        <v>92</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" t="s">
         <v>567</v>
       </c>
-      <c r="C107" t="s">
-        <v>93</v>
-      </c>
-      <c r="D107">
-        <v>1</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>568</v>
       </c>
-      <c r="G107" t="s">
+      <c r="H107" t="s">
         <v>569</v>
-      </c>
-      <c r="H107" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" t="s">
+        <v>570</v>
+      </c>
+      <c r="B108" t="s">
         <v>571</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
         <v>572</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108">
+        <v>1</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="D108">
-        <v>1</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F108" s="6" t="s">
+      <c r="G108" t="s">
         <v>574</v>
       </c>
-      <c r="G108" t="s">
+      <c r="H108" t="s">
         <v>575</v>
-      </c>
-      <c r="H108" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" t="s">
+        <v>576</v>
+      </c>
+      <c r="B109" t="s">
         <v>577</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>578</v>
-      </c>
-      <c r="C109" t="s">
-        <v>579</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -7184,18 +7184,18 @@
       </c>
       <c r="F109" s="6"/>
       <c r="G109" t="s">
+        <v>579</v>
+      </c>
+      <c r="H109" t="s">
         <v>580</v>
-      </c>
-      <c r="H109" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" t="s">
+        <v>581</v>
+      </c>
+      <c r="B110" t="s">
         <v>582</v>
-      </c>
-      <c r="B110" t="s">
-        <v>583</v>
       </c>
       <c r="C110" t="s">
         <v>17</v>
@@ -7208,18 +7208,18 @@
       </c>
       <c r="F110" s="6"/>
       <c r="G110" t="s">
+        <v>583</v>
+      </c>
+      <c r="H110" t="s">
         <v>584</v>
-      </c>
-      <c r="H110" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" t="s">
+        <v>585</v>
+      </c>
+      <c r="B111" t="s">
         <v>586</v>
-      </c>
-      <c r="B111" t="s">
-        <v>587</v>
       </c>
       <c r="C111" t="s">
         <v>10</v>
@@ -7231,24 +7231,24 @@
         <v>11</v>
       </c>
       <c r="F111" t="s">
+        <v>587</v>
+      </c>
+      <c r="G111" t="s">
         <v>588</v>
       </c>
-      <c r="G111" t="s">
+      <c r="H111" t="s">
         <v>589</v>
-      </c>
-      <c r="H111" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" t="s">
+        <v>590</v>
+      </c>
+      <c r="B112" t="s">
         <v>591</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>592</v>
-      </c>
-      <c r="C112" t="s">
-        <v>593</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -7258,21 +7258,21 @@
       </c>
       <c r="F112" s="6"/>
       <c r="G112" t="s">
+        <v>593</v>
+      </c>
+      <c r="H112" t="s">
         <v>594</v>
-      </c>
-      <c r="H112" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
+        <v>595</v>
+      </c>
+      <c r="B113" t="s">
         <v>596</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
         <v>597</v>
-      </c>
-      <c r="C113" t="s">
-        <v>598</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -7282,21 +7282,21 @@
       </c>
       <c r="F113" s="6"/>
       <c r="G113" t="s">
+        <v>598</v>
+      </c>
+      <c r="H113" t="s">
         <v>599</v>
-      </c>
-      <c r="H113" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" t="s">
+        <v>600</v>
+      </c>
+      <c r="B114" t="s">
         <v>601</v>
       </c>
-      <c r="B114" t="s">
-        <v>602</v>
-      </c>
       <c r="C114" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -7306,18 +7306,18 @@
       </c>
       <c r="F114" s="6"/>
       <c r="G114" t="s">
+        <v>602</v>
+      </c>
+      <c r="H114" t="s">
         <v>603</v>
-      </c>
-      <c r="H114" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
+        <v>604</v>
+      </c>
+      <c r="B115" t="s">
         <v>605</v>
-      </c>
-      <c r="B115" t="s">
-        <v>606</v>
       </c>
       <c r="C115" t="s">
         <v>58</v>
@@ -7330,18 +7330,18 @@
       </c>
       <c r="F115" s="6"/>
       <c r="G115" t="s">
+        <v>606</v>
+      </c>
+      <c r="H115" t="s">
         <v>607</v>
-      </c>
-      <c r="H115" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
+        <v>608</v>
+      </c>
+      <c r="B116" t="s">
         <v>609</v>
-      </c>
-      <c r="B116" t="s">
-        <v>610</v>
       </c>
       <c r="C116" t="s">
         <v>58</v>
@@ -7354,21 +7354,21 @@
       </c>
       <c r="F116" s="6"/>
       <c r="G116" t="s">
+        <v>610</v>
+      </c>
+      <c r="H116" t="s">
         <v>611</v>
-      </c>
-      <c r="H116" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
+        <v>612</v>
+      </c>
+      <c r="B117" t="s">
         <v>613</v>
       </c>
-      <c r="B117" t="s">
-        <v>614</v>
-      </c>
       <c r="C117" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -7378,21 +7378,21 @@
       </c>
       <c r="F117" s="6"/>
       <c r="G117" t="s">
+        <v>614</v>
+      </c>
+      <c r="H117" t="s">
         <v>615</v>
-      </c>
-      <c r="H117" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" t="s">
+        <v>616</v>
+      </c>
+      <c r="B118" t="s">
         <v>617</v>
       </c>
-      <c r="B118" t="s">
-        <v>618</v>
-      </c>
       <c r="C118" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -7402,18 +7402,18 @@
       </c>
       <c r="F118" s="6"/>
       <c r="G118" t="s">
+        <v>618</v>
+      </c>
+      <c r="H118" t="s">
         <v>619</v>
-      </c>
-      <c r="H118" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
+        <v>620</v>
+      </c>
+      <c r="B119" t="s">
         <v>621</v>
-      </c>
-      <c r="B119" t="s">
-        <v>622</v>
       </c>
       <c r="C119" t="s">
         <v>58</v>
@@ -7426,47 +7426,47 @@
       </c>
       <c r="F119" s="6"/>
       <c r="G119" t="s">
+        <v>622</v>
+      </c>
+      <c r="H119" t="s">
         <v>623</v>
-      </c>
-      <c r="H119" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
+        <v>624</v>
+      </c>
+      <c r="B120" t="s">
         <v>625</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" t="s">
+        <v>92</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F120" t="s">
         <v>626</v>
       </c>
-      <c r="C120" t="s">
-        <v>93</v>
-      </c>
-      <c r="D120">
-        <v>1</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F120" t="s">
+      <c r="G120" t="s">
         <v>627</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H120" t="s">
         <v>628</v>
-      </c>
-      <c r="H120" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
+        <v>629</v>
+      </c>
+      <c r="B121" t="s">
         <v>630</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121" t="s">
         <v>631</v>
-      </c>
-      <c r="C121" t="s">
-        <v>632</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -7476,18 +7476,18 @@
       </c>
       <c r="F121" s="6"/>
       <c r="G121" t="s">
+        <v>632</v>
+      </c>
+      <c r="H121" t="s">
         <v>633</v>
-      </c>
-      <c r="H121" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
+        <v>634</v>
+      </c>
+      <c r="B122" t="s">
         <v>635</v>
-      </c>
-      <c r="B122" t="s">
-        <v>636</v>
       </c>
       <c r="C122" t="s">
         <v>17</v>
@@ -7500,18 +7500,18 @@
       </c>
       <c r="F122" s="6"/>
       <c r="G122" t="s">
+        <v>636</v>
+      </c>
+      <c r="H122" t="s">
         <v>637</v>
-      </c>
-      <c r="H122" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
+        <v>638</v>
+      </c>
+      <c r="B123" t="s">
         <v>639</v>
-      </c>
-      <c r="B123" t="s">
-        <v>640</v>
       </c>
       <c r="C123" t="s">
         <v>17</v>
@@ -7524,18 +7524,18 @@
       </c>
       <c r="F123" s="6"/>
       <c r="G123" t="s">
+        <v>640</v>
+      </c>
+      <c r="H123" t="s">
         <v>641</v>
-      </c>
-      <c r="H123" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
+        <v>642</v>
+      </c>
+      <c r="B124" t="s">
         <v>643</v>
-      </c>
-      <c r="B124" t="s">
-        <v>644</v>
       </c>
       <c r="C124" t="s">
         <v>58</v>
@@ -7548,21 +7548,21 @@
       </c>
       <c r="F124" s="6"/>
       <c r="G124" t="s">
+        <v>644</v>
+      </c>
+      <c r="H124" t="s">
         <v>645</v>
-      </c>
-      <c r="H124" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
+        <v>646</v>
+      </c>
+      <c r="B125" t="s">
         <v>647</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
         <v>648</v>
-      </c>
-      <c r="C125" t="s">
-        <v>649</v>
       </c>
       <c r="D125">
         <v>4</v>
@@ -7572,21 +7572,21 @@
       </c>
       <c r="F125" s="6"/>
       <c r="G125" t="s">
+        <v>649</v>
+      </c>
+      <c r="H125" t="s">
         <v>650</v>
-      </c>
-      <c r="H125" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
+        <v>651</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C126" t="s">
         <v>652</v>
-      </c>
-      <c r="B126" t="s">
-        <v>1283</v>
-      </c>
-      <c r="C126" t="s">
-        <v>653</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -7596,73 +7596,73 @@
       </c>
       <c r="F126" s="6"/>
       <c r="G126" t="s">
+        <v>653</v>
+      </c>
+      <c r="H126" t="s">
         <v>654</v>
-      </c>
-      <c r="H126" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
+        <v>655</v>
+      </c>
+      <c r="B127" t="s">
         <v>656</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" t="s">
+        <v>394</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" t="s">
         <v>657</v>
       </c>
-      <c r="C127" t="s">
-        <v>395</v>
-      </c>
-      <c r="D127">
-        <v>1</v>
-      </c>
-      <c r="E127" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F127" t="s">
+      <c r="G127" t="s">
         <v>658</v>
       </c>
-      <c r="G127" t="s">
+      <c r="H127" t="s">
         <v>659</v>
-      </c>
-      <c r="H127" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
+        <v>660</v>
+      </c>
+      <c r="B128" t="s">
         <v>661</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
+        <v>414</v>
+      </c>
+      <c r="D128">
+        <v>1</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F128" t="s">
         <v>662</v>
       </c>
-      <c r="C128" t="s">
-        <v>415</v>
-      </c>
-      <c r="D128">
-        <v>1</v>
-      </c>
-      <c r="E128" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F128" t="s">
+      <c r="G128" t="s">
         <v>663</v>
       </c>
-      <c r="G128" t="s">
+      <c r="H128" t="s">
         <v>664</v>
-      </c>
-      <c r="H128" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
+        <v>665</v>
+      </c>
+      <c r="B129" t="s">
         <v>666</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>667</v>
-      </c>
-      <c r="C129" t="s">
-        <v>668</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -7672,21 +7672,21 @@
       </c>
       <c r="F129" s="6"/>
       <c r="G129" t="s">
+        <v>668</v>
+      </c>
+      <c r="H129" t="s">
         <v>669</v>
-      </c>
-      <c r="H129" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
+        <v>670</v>
+      </c>
+      <c r="B130" t="s">
         <v>671</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" t="s">
         <v>672</v>
-      </c>
-      <c r="C130" t="s">
-        <v>673</v>
       </c>
       <c r="D130">
         <v>4</v>
@@ -7696,21 +7696,21 @@
       </c>
       <c r="F130" s="6"/>
       <c r="G130" t="s">
+        <v>673</v>
+      </c>
+      <c r="H130" t="s">
         <v>674</v>
-      </c>
-      <c r="H130" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
+        <v>675</v>
+      </c>
+      <c r="B131" t="s">
         <v>676</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" t="s">
         <v>677</v>
-      </c>
-      <c r="C131" t="s">
-        <v>678</v>
       </c>
       <c r="D131">
         <v>2</v>
@@ -7719,24 +7719,24 @@
         <v>11</v>
       </c>
       <c r="F131" t="s">
+        <v>678</v>
+      </c>
+      <c r="G131" t="s">
         <v>679</v>
       </c>
-      <c r="G131" t="s">
+      <c r="H131" t="s">
         <v>680</v>
-      </c>
-      <c r="H131" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
+        <v>681</v>
+      </c>
+      <c r="B132" t="s">
         <v>682</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
         <v>683</v>
-      </c>
-      <c r="C132" t="s">
-        <v>684</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -7746,18 +7746,18 @@
       </c>
       <c r="F132" s="6"/>
       <c r="G132" t="s">
+        <v>684</v>
+      </c>
+      <c r="H132" t="s">
         <v>685</v>
-      </c>
-      <c r="H132" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
+        <v>686</v>
+      </c>
+      <c r="B133" t="s">
         <v>687</v>
-      </c>
-      <c r="B133" t="s">
-        <v>688</v>
       </c>
       <c r="C133" t="s">
         <v>10</v>
@@ -7770,21 +7770,21 @@
       </c>
       <c r="F133" s="6"/>
       <c r="G133" t="s">
+        <v>688</v>
+      </c>
+      <c r="H133" t="s">
         <v>689</v>
-      </c>
-      <c r="H133" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" t="s">
+        <v>690</v>
+      </c>
+      <c r="B134" t="s">
         <v>691</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" t="s">
         <v>692</v>
-      </c>
-      <c r="C134" t="s">
-        <v>693</v>
       </c>
       <c r="D134">
         <v>2</v>
@@ -7793,21 +7793,21 @@
         <v>18</v>
       </c>
       <c r="F134" t="s">
+        <v>693</v>
+      </c>
+      <c r="G134" t="s">
         <v>694</v>
       </c>
-      <c r="G134" t="s">
+      <c r="H134" t="s">
         <v>695</v>
-      </c>
-      <c r="H134" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" t="s">
+        <v>696</v>
+      </c>
+      <c r="B135" t="s">
         <v>697</v>
-      </c>
-      <c r="B135" t="s">
-        <v>698</v>
       </c>
       <c r="C135" t="s">
         <v>58</v>
@@ -7819,47 +7819,47 @@
         <v>11</v>
       </c>
       <c r="F135" t="s">
+        <v>698</v>
+      </c>
+      <c r="G135" t="s">
         <v>699</v>
       </c>
-      <c r="G135" t="s">
+      <c r="H135" t="s">
         <v>700</v>
-      </c>
-      <c r="H135" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" t="s">
+        <v>701</v>
+      </c>
+      <c r="B136" t="s">
         <v>702</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
         <v>703</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F136" t="s">
         <v>704</v>
       </c>
-      <c r="D136">
-        <v>1</v>
-      </c>
-      <c r="E136" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F136" t="s">
+      <c r="G136" t="s">
         <v>705</v>
       </c>
-      <c r="G136" t="s">
+      <c r="H136" t="s">
         <v>706</v>
-      </c>
-      <c r="H136" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
+        <v>707</v>
+      </c>
+      <c r="B137" t="s">
         <v>708</v>
-      </c>
-      <c r="B137" t="s">
-        <v>709</v>
       </c>
       <c r="C137" t="s">
         <v>58</v>
@@ -7872,21 +7872,21 @@
       </c>
       <c r="F137" s="6"/>
       <c r="G137" t="s">
+        <v>709</v>
+      </c>
+      <c r="H137" t="s">
         <v>710</v>
-      </c>
-      <c r="H137" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" t="s">
+        <v>711</v>
+      </c>
+      <c r="B138" t="s">
         <v>712</v>
       </c>
-      <c r="B138" t="s">
-        <v>713</v>
-      </c>
       <c r="C138" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -7896,18 +7896,18 @@
       </c>
       <c r="F138" s="6"/>
       <c r="G138" t="s">
+        <v>713</v>
+      </c>
+      <c r="H138" t="s">
         <v>714</v>
-      </c>
-      <c r="H138" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" t="s">
+        <v>715</v>
+      </c>
+      <c r="B139" t="s">
         <v>716</v>
-      </c>
-      <c r="B139" t="s">
-        <v>717</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
@@ -7920,21 +7920,21 @@
       </c>
       <c r="F139" s="6"/>
       <c r="G139" t="s">
+        <v>717</v>
+      </c>
+      <c r="H139" t="s">
         <v>718</v>
-      </c>
-      <c r="H139" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
+        <v>719</v>
+      </c>
+      <c r="B140" t="s">
         <v>720</v>
       </c>
-      <c r="B140" t="s">
-        <v>721</v>
-      </c>
       <c r="C140" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -7944,18 +7944,18 @@
       </c>
       <c r="F140" s="6"/>
       <c r="G140" t="s">
+        <v>721</v>
+      </c>
+      <c r="H140" t="s">
         <v>722</v>
-      </c>
-      <c r="H140" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" t="s">
+        <v>723</v>
+      </c>
+      <c r="B141" t="s">
         <v>724</v>
-      </c>
-      <c r="B141" t="s">
-        <v>725</v>
       </c>
       <c r="C141" t="s">
         <v>10</v>
@@ -7968,21 +7968,21 @@
       </c>
       <c r="F141" s="6"/>
       <c r="G141" t="s">
+        <v>725</v>
+      </c>
+      <c r="H141" t="s">
         <v>726</v>
-      </c>
-      <c r="H141" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" t="s">
+        <v>727</v>
+      </c>
+      <c r="B142" t="s">
         <v>728</v>
       </c>
-      <c r="B142" t="s">
-        <v>729</v>
-      </c>
       <c r="C142" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -7992,21 +7992,21 @@
       </c>
       <c r="F142" s="6"/>
       <c r="G142" t="s">
+        <v>729</v>
+      </c>
+      <c r="H142" t="s">
         <v>730</v>
-      </c>
-      <c r="H142" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" t="s">
+        <v>731</v>
+      </c>
+      <c r="B143" t="s">
         <v>732</v>
       </c>
-      <c r="B143" t="s">
-        <v>733</v>
-      </c>
       <c r="C143" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D143">
         <v>2</v>
@@ -8016,21 +8016,21 @@
       </c>
       <c r="F143" s="6"/>
       <c r="G143" t="s">
+        <v>733</v>
+      </c>
+      <c r="H143" t="s">
         <v>734</v>
-      </c>
-      <c r="H143" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" t="s">
+        <v>735</v>
+      </c>
+      <c r="B144" t="s">
         <v>736</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
         <v>737</v>
-      </c>
-      <c r="C144" t="s">
-        <v>738</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -8040,18 +8040,18 @@
       </c>
       <c r="F144" s="6"/>
       <c r="G144" t="s">
+        <v>738</v>
+      </c>
+      <c r="H144" t="s">
         <v>739</v>
-      </c>
-      <c r="H144" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" t="s">
+        <v>740</v>
+      </c>
+      <c r="B145" t="s">
         <v>741</v>
-      </c>
-      <c r="B145" t="s">
-        <v>742</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -8064,99 +8064,99 @@
       </c>
       <c r="F145" s="6"/>
       <c r="G145" t="s">
+        <v>742</v>
+      </c>
+      <c r="H145" t="s">
         <v>743</v>
-      </c>
-      <c r="H145" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
+        <v>744</v>
+      </c>
+      <c r="B146" t="s">
         <v>745</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C146" t="s">
         <v>746</v>
       </c>
-      <c r="C146" t="s">
+      <c r="D146">
+        <v>1</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F146" t="s">
         <v>747</v>
       </c>
-      <c r="D146">
-        <v>1</v>
-      </c>
-      <c r="E146" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>748</v>
       </c>
-      <c r="G146" t="s">
+      <c r="H146" t="s">
         <v>749</v>
-      </c>
-      <c r="H146" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
+        <v>750</v>
+      </c>
+      <c r="B147" t="s">
         <v>751</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C147" t="s">
+        <v>254</v>
+      </c>
+      <c r="D147">
+        <v>1</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" t="s">
         <v>752</v>
       </c>
-      <c r="C147" t="s">
-        <v>255</v>
-      </c>
-      <c r="D147">
-        <v>1</v>
-      </c>
-      <c r="E147" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F147" t="s">
+      <c r="G147" t="s">
         <v>753</v>
       </c>
-      <c r="G147" t="s">
+      <c r="H147" t="s">
         <v>754</v>
-      </c>
-      <c r="H147" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" t="s">
+        <v>755</v>
+      </c>
+      <c r="B148" t="s">
         <v>756</v>
       </c>
-      <c r="B148" t="s">
+      <c r="C148" t="s">
         <v>757</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D148">
+        <v>1</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" t="s">
         <v>758</v>
       </c>
-      <c r="D148">
-        <v>1</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F148" t="s">
+      <c r="G148" t="s">
         <v>759</v>
       </c>
-      <c r="G148" t="s">
+      <c r="H148" t="s">
         <v>760</v>
-      </c>
-      <c r="H148" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
+        <v>761</v>
+      </c>
+      <c r="B149" t="s">
         <v>762</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" t="s">
         <v>763</v>
-      </c>
-      <c r="C149" t="s">
-        <v>764</v>
       </c>
       <c r="D149">
         <v>2</v>
@@ -8166,21 +8166,21 @@
       </c>
       <c r="F149" s="6"/>
       <c r="G149" t="s">
+        <v>764</v>
+      </c>
+      <c r="H149" t="s">
         <v>765</v>
-      </c>
-      <c r="H149" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
+        <v>766</v>
+      </c>
+      <c r="B150" t="s">
         <v>767</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C150" t="s">
         <v>768</v>
-      </c>
-      <c r="C150" t="s">
-        <v>769</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -8190,21 +8190,21 @@
       </c>
       <c r="F150" s="6"/>
       <c r="G150" t="s">
+        <v>769</v>
+      </c>
+      <c r="H150" t="s">
         <v>770</v>
-      </c>
-      <c r="H150" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
+        <v>771</v>
+      </c>
+      <c r="B151" t="s">
         <v>772</v>
       </c>
-      <c r="B151" t="s">
-        <v>773</v>
-      </c>
       <c r="C151" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -8214,21 +8214,21 @@
       </c>
       <c r="F151" s="6"/>
       <c r="G151" t="s">
+        <v>773</v>
+      </c>
+      <c r="H151" t="s">
         <v>774</v>
-      </c>
-      <c r="H151" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" t="s">
+        <v>775</v>
+      </c>
+      <c r="B152" t="s">
         <v>776</v>
       </c>
-      <c r="B152" t="s">
-        <v>777</v>
-      </c>
       <c r="C152" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -8238,21 +8238,21 @@
       </c>
       <c r="F152" s="6"/>
       <c r="G152" t="s">
+        <v>777</v>
+      </c>
+      <c r="H152" t="s">
         <v>778</v>
-      </c>
-      <c r="H152" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B153" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C153" t="s">
         <v>1281</v>
-      </c>
-      <c r="C153" t="s">
-        <v>1282</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -8266,36 +8266,36 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
+        <v>780</v>
+      </c>
+      <c r="B154" t="s">
         <v>781</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C154" t="s">
         <v>782</v>
       </c>
-      <c r="C154" t="s">
+      <c r="D154">
+        <v>1</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154" t="s">
         <v>783</v>
       </c>
-      <c r="D154">
-        <v>1</v>
-      </c>
-      <c r="E154" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F154" t="s">
+      <c r="G154" t="s">
         <v>784</v>
       </c>
-      <c r="G154" t="s">
+      <c r="H154" t="s">
         <v>785</v>
-      </c>
-      <c r="H154" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
+        <v>786</v>
+      </c>
+      <c r="B155" t="s">
         <v>787</v>
-      </c>
-      <c r="B155" t="s">
-        <v>788</v>
       </c>
       <c r="C155" t="s">
         <v>58</v>
@@ -8308,21 +8308,21 @@
       </c>
       <c r="F155" s="6"/>
       <c r="G155" t="s">
+        <v>788</v>
+      </c>
+      <c r="H155" t="s">
         <v>789</v>
-      </c>
-      <c r="H155" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
+        <v>790</v>
+      </c>
+      <c r="B156" t="s">
         <v>791</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C156" t="s">
         <v>792</v>
-      </c>
-      <c r="C156" t="s">
-        <v>793</v>
       </c>
       <c r="D156">
         <v>1</v>
@@ -8332,18 +8332,18 @@
       </c>
       <c r="F156" s="6"/>
       <c r="G156" t="s">
+        <v>793</v>
+      </c>
+      <c r="H156" t="s">
         <v>794</v>
-      </c>
-      <c r="H156" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
+        <v>795</v>
+      </c>
+      <c r="B157" t="s">
         <v>796</v>
-      </c>
-      <c r="B157" t="s">
-        <v>797</v>
       </c>
       <c r="C157" t="s">
         <v>58</v>
@@ -8356,21 +8356,21 @@
       </c>
       <c r="F157" s="6"/>
       <c r="G157" t="s">
+        <v>797</v>
+      </c>
+      <c r="H157" t="s">
         <v>798</v>
-      </c>
-      <c r="H157" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
+        <v>799</v>
+      </c>
+      <c r="B158" t="s">
         <v>800</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C158" t="s">
         <v>801</v>
-      </c>
-      <c r="C158" t="s">
-        <v>802</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -8380,21 +8380,21 @@
       </c>
       <c r="F158" s="6"/>
       <c r="G158" t="s">
+        <v>802</v>
+      </c>
+      <c r="H158" t="s">
         <v>803</v>
-      </c>
-      <c r="H158" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
+        <v>804</v>
+      </c>
+      <c r="B159" t="s">
         <v>805</v>
       </c>
-      <c r="B159" t="s">
-        <v>806</v>
-      </c>
       <c r="C159" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -8406,13 +8406,13 @@
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
+        <v>806</v>
+      </c>
+      <c r="B160" t="s">
         <v>807</v>
       </c>
-      <c r="B160" t="s">
+      <c r="C160" t="s">
         <v>808</v>
-      </c>
-      <c r="C160" t="s">
-        <v>809</v>
       </c>
       <c r="D160">
         <v>1</v>
@@ -8422,21 +8422,21 @@
       </c>
       <c r="F160" s="6"/>
       <c r="G160" t="s">
+        <v>809</v>
+      </c>
+      <c r="H160" t="s">
         <v>810</v>
-      </c>
-      <c r="H160" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
+        <v>811</v>
+      </c>
+      <c r="B161" t="s">
         <v>812</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C161" t="s">
         <v>813</v>
-      </c>
-      <c r="C161" t="s">
-        <v>814</v>
       </c>
       <c r="D161">
         <v>2</v>
@@ -8445,24 +8445,24 @@
         <v>18</v>
       </c>
       <c r="F161" t="s">
+        <v>814</v>
+      </c>
+      <c r="G161" t="s">
         <v>815</v>
       </c>
-      <c r="G161" t="s">
+      <c r="H161" t="s">
         <v>816</v>
-      </c>
-      <c r="H161" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
+        <v>817</v>
+      </c>
+      <c r="B162" t="s">
         <v>818</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C162" t="s">
         <v>819</v>
-      </c>
-      <c r="C162" t="s">
-        <v>820</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -8472,18 +8472,18 @@
       </c>
       <c r="F162" s="6"/>
       <c r="G162" t="s">
+        <v>820</v>
+      </c>
+      <c r="H162" t="s">
         <v>821</v>
-      </c>
-      <c r="H162" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
+        <v>822</v>
+      </c>
+      <c r="B163" t="s">
         <v>823</v>
-      </c>
-      <c r="B163" t="s">
-        <v>824</v>
       </c>
       <c r="C163" t="s">
         <v>17</v>
@@ -8496,18 +8496,18 @@
       </c>
       <c r="F163" s="6"/>
       <c r="G163" t="s">
+        <v>824</v>
+      </c>
+      <c r="H163" t="s">
         <v>825</v>
-      </c>
-      <c r="H163" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
+        <v>826</v>
+      </c>
+      <c r="B164" t="s">
         <v>827</v>
-      </c>
-      <c r="B164" t="s">
-        <v>828</v>
       </c>
       <c r="C164" t="s">
         <v>58</v>
@@ -8520,21 +8520,21 @@
       </c>
       <c r="F164" s="6"/>
       <c r="G164" t="s">
+        <v>828</v>
+      </c>
+      <c r="H164" t="s">
         <v>829</v>
-      </c>
-      <c r="H164" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
+        <v>830</v>
+      </c>
+      <c r="B165" t="s">
         <v>831</v>
       </c>
-      <c r="B165" t="s">
+      <c r="C165" t="s">
         <v>832</v>
-      </c>
-      <c r="C165" t="s">
-        <v>833</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -8544,18 +8544,18 @@
       </c>
       <c r="F165" s="6"/>
       <c r="G165" t="s">
+        <v>833</v>
+      </c>
+      <c r="H165" t="s">
         <v>834</v>
-      </c>
-      <c r="H165" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
+        <v>835</v>
+      </c>
+      <c r="B166" t="s">
         <v>836</v>
-      </c>
-      <c r="B166" t="s">
-        <v>837</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
@@ -8568,18 +8568,18 @@
       </c>
       <c r="F166" s="6"/>
       <c r="G166" t="s">
+        <v>837</v>
+      </c>
+      <c r="H166" t="s">
         <v>838</v>
-      </c>
-      <c r="H166" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
+        <v>839</v>
+      </c>
+      <c r="B167" t="s">
         <v>840</v>
-      </c>
-      <c r="B167" t="s">
-        <v>841</v>
       </c>
       <c r="C167" t="s">
         <v>58</v>
@@ -8592,47 +8592,47 @@
       </c>
       <c r="F167" s="6"/>
       <c r="G167" t="s">
+        <v>841</v>
+      </c>
+      <c r="H167" t="s">
         <v>842</v>
-      </c>
-      <c r="H167" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
+        <v>843</v>
+      </c>
+      <c r="B168" t="s">
         <v>844</v>
       </c>
-      <c r="B168" t="s">
+      <c r="C168" t="s">
+        <v>92</v>
+      </c>
+      <c r="D168">
+        <v>1</v>
+      </c>
+      <c r="E168" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F168" t="s">
         <v>845</v>
       </c>
-      <c r="C168" t="s">
-        <v>93</v>
-      </c>
-      <c r="D168">
-        <v>1</v>
-      </c>
-      <c r="E168" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F168" t="s">
+      <c r="G168" t="s">
         <v>846</v>
       </c>
-      <c r="G168" t="s">
+      <c r="H168" t="s">
         <v>847</v>
-      </c>
-      <c r="H168" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
+        <v>848</v>
+      </c>
+      <c r="B169" t="s">
         <v>849</v>
       </c>
-      <c r="B169" t="s">
+      <c r="C169" t="s">
         <v>850</v>
-      </c>
-      <c r="C169" t="s">
-        <v>851</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -8642,18 +8642,18 @@
       </c>
       <c r="F169" s="6"/>
       <c r="G169" t="s">
+        <v>851</v>
+      </c>
+      <c r="H169" t="s">
         <v>852</v>
-      </c>
-      <c r="H169" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
+        <v>853</v>
+      </c>
+      <c r="B170" t="s">
         <v>854</v>
-      </c>
-      <c r="B170" t="s">
-        <v>855</v>
       </c>
       <c r="C170" t="s">
         <v>17</v>
@@ -8666,47 +8666,47 @@
       </c>
       <c r="F170" s="6"/>
       <c r="G170" t="s">
+        <v>855</v>
+      </c>
+      <c r="H170" t="s">
         <v>856</v>
-      </c>
-      <c r="H170" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
+        <v>857</v>
+      </c>
+      <c r="B171" t="s">
         <v>858</v>
       </c>
-      <c r="B171" t="s">
+      <c r="C171" t="s">
+        <v>737</v>
+      </c>
+      <c r="D171">
+        <v>1</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171" t="s">
         <v>859</v>
       </c>
-      <c r="C171" t="s">
-        <v>738</v>
-      </c>
-      <c r="D171">
-        <v>1</v>
-      </c>
-      <c r="E171" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F171" t="s">
+      <c r="G171" t="s">
         <v>860</v>
       </c>
-      <c r="G171" t="s">
+      <c r="H171" t="s">
         <v>861</v>
-      </c>
-      <c r="H171" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
+        <v>862</v>
+      </c>
+      <c r="B172" t="s">
         <v>863</v>
       </c>
-      <c r="B172" t="s">
+      <c r="C172" t="s">
         <v>864</v>
-      </c>
-      <c r="C172" t="s">
-        <v>865</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -8716,21 +8716,21 @@
       </c>
       <c r="F172" s="6"/>
       <c r="G172" t="s">
+        <v>865</v>
+      </c>
+      <c r="H172" t="s">
         <v>866</v>
-      </c>
-      <c r="H172" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
+        <v>867</v>
+      </c>
+      <c r="B173" t="s">
         <v>868</v>
       </c>
-      <c r="B173" t="s">
+      <c r="C173" t="s">
         <v>869</v>
-      </c>
-      <c r="C173" t="s">
-        <v>870</v>
       </c>
       <c r="D173">
         <v>2</v>
@@ -8739,24 +8739,24 @@
         <v>11</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G173" t="s">
+        <v>870</v>
+      </c>
+      <c r="H173" t="s">
         <v>871</v>
-      </c>
-      <c r="H173" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
+        <v>872</v>
+      </c>
+      <c r="B174" t="s">
         <v>873</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
         <v>874</v>
-      </c>
-      <c r="C174" t="s">
-        <v>875</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -8766,18 +8766,18 @@
       </c>
       <c r="F174" s="6"/>
       <c r="G174" t="s">
+        <v>875</v>
+      </c>
+      <c r="H174" t="s">
         <v>876</v>
-      </c>
-      <c r="H174" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
+        <v>877</v>
+      </c>
+      <c r="B175" t="s">
         <v>878</v>
-      </c>
-      <c r="B175" t="s">
-        <v>879</v>
       </c>
       <c r="C175" t="s">
         <v>17</v>
@@ -8790,21 +8790,21 @@
       </c>
       <c r="F175" s="6"/>
       <c r="G175" t="s">
+        <v>879</v>
+      </c>
+      <c r="H175" t="s">
         <v>880</v>
-      </c>
-      <c r="H175" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
+        <v>881</v>
+      </c>
+      <c r="B176" t="s">
         <v>882</v>
       </c>
-      <c r="B176" t="s">
-        <v>883</v>
-      </c>
       <c r="C176" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -8814,18 +8814,18 @@
       </c>
       <c r="F176" s="6"/>
       <c r="G176" t="s">
+        <v>883</v>
+      </c>
+      <c r="H176" t="s">
         <v>884</v>
-      </c>
-      <c r="H176" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
+        <v>885</v>
+      </c>
+      <c r="B177" t="s">
         <v>886</v>
-      </c>
-      <c r="B177" t="s">
-        <v>887</v>
       </c>
       <c r="C177" t="s">
         <v>58</v>
@@ -8838,21 +8838,21 @@
       </c>
       <c r="F177" s="6"/>
       <c r="G177" t="s">
+        <v>887</v>
+      </c>
+      <c r="H177" t="s">
         <v>888</v>
-      </c>
-      <c r="H177" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
+        <v>889</v>
+      </c>
+      <c r="B178" t="s">
         <v>890</v>
       </c>
-      <c r="B178" t="s">
-        <v>891</v>
-      </c>
       <c r="C178" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D178">
         <v>1</v>
@@ -8862,18 +8862,18 @@
       </c>
       <c r="F178" s="6"/>
       <c r="G178" t="s">
+        <v>891</v>
+      </c>
+      <c r="H178" t="s">
         <v>892</v>
-      </c>
-      <c r="H178" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
+        <v>893</v>
+      </c>
+      <c r="B179" t="s">
         <v>894</v>
-      </c>
-      <c r="B179" t="s">
-        <v>895</v>
       </c>
       <c r="C179" t="s">
         <v>10</v>
@@ -8886,21 +8886,21 @@
       </c>
       <c r="F179" s="6"/>
       <c r="G179" t="s">
+        <v>895</v>
+      </c>
+      <c r="H179" t="s">
         <v>896</v>
-      </c>
-      <c r="H179" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" t="s">
+        <v>897</v>
+      </c>
+      <c r="B180" t="s">
         <v>898</v>
       </c>
-      <c r="B180" t="s">
-        <v>899</v>
-      </c>
       <c r="C180" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D180">
         <v>1</v>
@@ -8912,13 +8912,13 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
+        <v>899</v>
+      </c>
+      <c r="B181" t="s">
         <v>900</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
         <v>901</v>
-      </c>
-      <c r="C181" t="s">
-        <v>902</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -8928,18 +8928,18 @@
       </c>
       <c r="F181" s="6"/>
       <c r="G181" t="s">
+        <v>902</v>
+      </c>
+      <c r="H181" t="s">
         <v>903</v>
-      </c>
-      <c r="H181" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
+        <v>904</v>
+      </c>
+      <c r="B182" t="s">
         <v>905</v>
-      </c>
-      <c r="B182" t="s">
-        <v>906</v>
       </c>
       <c r="C182" t="s">
         <v>58</v>
@@ -8952,21 +8952,21 @@
       </c>
       <c r="F182" s="6"/>
       <c r="G182" t="s">
+        <v>906</v>
+      </c>
+      <c r="H182" t="s">
         <v>907</v>
-      </c>
-      <c r="H182" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
+        <v>908</v>
+      </c>
+      <c r="B183" t="s">
         <v>909</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
         <v>910</v>
-      </c>
-      <c r="C183" t="s">
-        <v>911</v>
       </c>
       <c r="D183">
         <v>2</v>
@@ -8976,21 +8976,21 @@
       </c>
       <c r="F183" s="6"/>
       <c r="G183" t="s">
+        <v>911</v>
+      </c>
+      <c r="H183" t="s">
         <v>912</v>
-      </c>
-      <c r="H183" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
+        <v>913</v>
+      </c>
+      <c r="B184" t="s">
         <v>914</v>
       </c>
-      <c r="B184" t="s">
+      <c r="C184" t="s">
         <v>915</v>
-      </c>
-      <c r="C184" t="s">
-        <v>916</v>
       </c>
       <c r="D184">
         <v>1</v>
@@ -9000,21 +9000,21 @@
       </c>
       <c r="F184" s="6"/>
       <c r="G184" t="s">
+        <v>916</v>
+      </c>
+      <c r="H184" t="s">
         <v>917</v>
-      </c>
-      <c r="H184" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
+        <v>918</v>
+      </c>
+      <c r="B185" t="s">
         <v>919</v>
       </c>
-      <c r="B185" t="s">
+      <c r="C185" t="s">
         <v>920</v>
-      </c>
-      <c r="C185" t="s">
-        <v>921</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -9024,44 +9024,44 @@
       </c>
       <c r="F185" s="6"/>
       <c r="G185" t="s">
+        <v>921</v>
+      </c>
+      <c r="H185" t="s">
         <v>922</v>
-      </c>
-      <c r="H185" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
+        <v>923</v>
+      </c>
+      <c r="B186" t="s">
         <v>924</v>
       </c>
-      <c r="B186" t="s">
+      <c r="C186" t="s">
         <v>925</v>
       </c>
-      <c r="C186" t="s">
+      <c r="D186">
+        <v>1</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F186" t="s">
         <v>926</v>
       </c>
-      <c r="D186">
-        <v>1</v>
-      </c>
-      <c r="E186" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>927</v>
       </c>
-      <c r="G186" t="s">
+      <c r="H186" t="s">
         <v>928</v>
-      </c>
-      <c r="H186" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
+        <v>929</v>
+      </c>
+      <c r="B187" t="s">
         <v>930</v>
-      </c>
-      <c r="B187" t="s">
-        <v>931</v>
       </c>
       <c r="C187" t="s">
         <v>58</v>
@@ -9074,18 +9074,18 @@
       </c>
       <c r="F187" s="6"/>
       <c r="G187" t="s">
+        <v>931</v>
+      </c>
+      <c r="H187" t="s">
         <v>932</v>
-      </c>
-      <c r="H187" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
+        <v>933</v>
+      </c>
+      <c r="B188" t="s">
         <v>934</v>
-      </c>
-      <c r="B188" t="s">
-        <v>935</v>
       </c>
       <c r="C188" t="s">
         <v>58</v>
@@ -9098,21 +9098,21 @@
       </c>
       <c r="F188" s="6"/>
       <c r="G188" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H188" s="7" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
+        <v>936</v>
+      </c>
+      <c r="B189" t="s">
         <v>937</v>
       </c>
-      <c r="B189" t="s">
-        <v>938</v>
-      </c>
       <c r="C189" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -9122,21 +9122,21 @@
       </c>
       <c r="F189" s="6"/>
       <c r="G189" t="s">
+        <v>938</v>
+      </c>
+      <c r="H189" t="s">
         <v>939</v>
-      </c>
-      <c r="H189" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" t="s">
+        <v>940</v>
+      </c>
+      <c r="B190" t="s">
         <v>941</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C190" t="s">
         <v>942</v>
-      </c>
-      <c r="C190" t="s">
-        <v>943</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -9146,47 +9146,47 @@
       </c>
       <c r="F190" s="6"/>
       <c r="G190" t="s">
+        <v>943</v>
+      </c>
+      <c r="H190" t="s">
         <v>944</v>
-      </c>
-      <c r="H190" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" t="s">
+        <v>945</v>
+      </c>
+      <c r="B191" t="s">
         <v>946</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" t="s">
+        <v>792</v>
+      </c>
+      <c r="D191">
+        <v>1</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F191" t="s">
         <v>947</v>
       </c>
-      <c r="C191" t="s">
-        <v>793</v>
-      </c>
-      <c r="D191">
-        <v>1</v>
-      </c>
-      <c r="E191" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>948</v>
       </c>
-      <c r="G191" t="s">
+      <c r="H191" t="s">
         <v>949</v>
-      </c>
-      <c r="H191" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" t="s">
+        <v>950</v>
+      </c>
+      <c r="B192" t="s">
         <v>951</v>
       </c>
-      <c r="B192" t="s">
+      <c r="C192" t="s">
         <v>952</v>
-      </c>
-      <c r="C192" t="s">
-        <v>953</v>
       </c>
       <c r="D192">
         <v>1</v>
@@ -9196,18 +9196,18 @@
       </c>
       <c r="F192" s="6"/>
       <c r="G192" t="s">
+        <v>953</v>
+      </c>
+      <c r="H192" t="s">
         <v>954</v>
-      </c>
-      <c r="H192" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
+        <v>955</v>
+      </c>
+      <c r="B193" t="s">
         <v>956</v>
-      </c>
-      <c r="B193" t="s">
-        <v>957</v>
       </c>
       <c r="C193" t="s">
         <v>17</v>
@@ -9220,21 +9220,21 @@
       </c>
       <c r="F193" s="6"/>
       <c r="G193" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H193" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
+        <v>958</v>
+      </c>
+      <c r="B194" t="s">
         <v>959</v>
       </c>
-      <c r="B194" t="s">
-        <v>960</v>
-      </c>
       <c r="C194" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -9244,10 +9244,10 @@
       </c>
       <c r="F194" s="6"/>
       <c r="G194" t="s">
+        <v>960</v>
+      </c>
+      <c r="H194" t="s">
         <v>961</v>
-      </c>
-      <c r="H194" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="195" spans="1:8" s="1" customFormat="1">
@@ -9255,7 +9255,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>17</v>
@@ -9268,18 +9268,18 @@
       </c>
       <c r="F195" s="2"/>
       <c r="G195" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
+        <v>964</v>
+      </c>
+      <c r="B196" t="s">
         <v>965</v>
       </c>
-      <c r="B196" t="s">
+      <c r="C196" t="s">
         <v>966</v>
-      </c>
-      <c r="C196" t="s">
-        <v>967</v>
       </c>
       <c r="D196">
         <v>1</v>
@@ -9289,18 +9289,18 @@
       </c>
       <c r="F196" s="6"/>
       <c r="G196" t="s">
+        <v>967</v>
+      </c>
+      <c r="H196" t="s">
         <v>968</v>
-      </c>
-      <c r="H196" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" t="s">
+        <v>969</v>
+      </c>
+      <c r="B197" t="s">
         <v>970</v>
-      </c>
-      <c r="B197" t="s">
-        <v>971</v>
       </c>
       <c r="C197" t="s">
         <v>58</v>
@@ -9313,18 +9313,18 @@
       </c>
       <c r="F197" s="6"/>
       <c r="G197" t="s">
+        <v>971</v>
+      </c>
+      <c r="H197" t="s">
         <v>972</v>
-      </c>
-      <c r="H197" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" t="s">
+        <v>973</v>
+      </c>
+      <c r="B198" t="s">
         <v>974</v>
-      </c>
-      <c r="B198" t="s">
-        <v>975</v>
       </c>
       <c r="C198" t="s">
         <v>58</v>
@@ -9339,10 +9339,10 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
+        <v>975</v>
+      </c>
+      <c r="B199" t="s">
         <v>976</v>
-      </c>
-      <c r="B199" t="s">
-        <v>977</v>
       </c>
       <c r="C199" t="s">
         <v>58</v>
@@ -9355,18 +9355,18 @@
       </c>
       <c r="F199" s="6"/>
       <c r="G199" t="s">
+        <v>977</v>
+      </c>
+      <c r="H199" t="s">
         <v>978</v>
-      </c>
-      <c r="H199" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
+        <v>979</v>
+      </c>
+      <c r="B200" t="s">
         <v>980</v>
-      </c>
-      <c r="B200" t="s">
-        <v>981</v>
       </c>
       <c r="C200" t="s">
         <v>17</v>
@@ -9378,21 +9378,21 @@
         <v>18</v>
       </c>
       <c r="F200" t="s">
+        <v>981</v>
+      </c>
+      <c r="G200" t="s">
         <v>982</v>
       </c>
-      <c r="G200" t="s">
+      <c r="H200" t="s">
         <v>983</v>
-      </c>
-      <c r="H200" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
+        <v>984</v>
+      </c>
+      <c r="B201" t="s">
         <v>985</v>
-      </c>
-      <c r="B201" t="s">
-        <v>986</v>
       </c>
       <c r="C201" t="s">
         <v>10</v>
@@ -9405,21 +9405,21 @@
       </c>
       <c r="F201" s="6"/>
       <c r="G201" t="s">
+        <v>986</v>
+      </c>
+      <c r="H201" t="s">
         <v>987</v>
-      </c>
-      <c r="H201" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
+        <v>988</v>
+      </c>
+      <c r="B202" t="s">
         <v>989</v>
       </c>
-      <c r="B202" t="s">
-        <v>990</v>
-      </c>
       <c r="C202" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D202">
         <v>1</v>
@@ -9429,21 +9429,21 @@
       </c>
       <c r="F202" s="6"/>
       <c r="G202" t="s">
+        <v>990</v>
+      </c>
+      <c r="H202" t="s">
         <v>991</v>
-      </c>
-      <c r="H202" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
+        <v>992</v>
+      </c>
+      <c r="B203" t="s">
         <v>993</v>
       </c>
-      <c r="B203" t="s">
-        <v>994</v>
-      </c>
       <c r="C203" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -9453,21 +9453,21 @@
       </c>
       <c r="F203" s="6"/>
       <c r="G203" t="s">
+        <v>994</v>
+      </c>
+      <c r="H203" t="s">
         <v>995</v>
-      </c>
-      <c r="H203" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" t="s">
+        <v>996</v>
+      </c>
+      <c r="B204" t="s">
         <v>997</v>
       </c>
-      <c r="B204" t="s">
+      <c r="C204" t="s">
         <v>998</v>
-      </c>
-      <c r="C204" t="s">
-        <v>999</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -9477,18 +9477,18 @@
       </c>
       <c r="F204" s="6"/>
       <c r="G204" t="s">
+        <v>999</v>
+      </c>
+      <c r="H204" t="s">
         <v>1000</v>
-      </c>
-      <c r="H204" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B205" t="s">
         <v>1002</v>
-      </c>
-      <c r="B205" t="s">
-        <v>1003</v>
       </c>
       <c r="C205" t="s">
         <v>17</v>
@@ -9501,21 +9501,21 @@
       </c>
       <c r="F205" s="6"/>
       <c r="G205" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H205" t="s">
         <v>1004</v>
-      </c>
-      <c r="H205" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B206" t="s">
         <v>1006</v>
       </c>
-      <c r="B206" t="s">
+      <c r="C206" t="s">
         <v>1007</v>
-      </c>
-      <c r="C206" t="s">
-        <v>1008</v>
       </c>
       <c r="D206">
         <v>1</v>
@@ -9525,21 +9525,21 @@
       </c>
       <c r="F206" s="6"/>
       <c r="G206" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H206" t="s">
         <v>1009</v>
-      </c>
-      <c r="H206" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B207" t="s">
         <v>1011</v>
       </c>
-      <c r="B207" t="s">
-        <v>1012</v>
-      </c>
       <c r="C207" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D207">
         <v>1</v>
@@ -9549,21 +9549,21 @@
       </c>
       <c r="F207" s="6"/>
       <c r="G207" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H207" t="s">
         <v>1013</v>
-      </c>
-      <c r="H207" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B208" t="s">
         <v>1015</v>
       </c>
-      <c r="B208" t="s">
-        <v>1016</v>
-      </c>
       <c r="C208" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -9573,21 +9573,21 @@
       </c>
       <c r="F208" s="6"/>
       <c r="G208" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H208" t="s">
         <v>1017</v>
-      </c>
-      <c r="H208" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B209" t="s">
         <v>1019</v>
       </c>
-      <c r="B209" t="s">
+      <c r="C209" t="s">
         <v>1020</v>
-      </c>
-      <c r="C209" t="s">
-        <v>1021</v>
       </c>
       <c r="D209">
         <v>1</v>
@@ -9597,21 +9597,21 @@
       </c>
       <c r="F209" s="6"/>
       <c r="G209" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H209" t="s">
         <v>1022</v>
-      </c>
-      <c r="H209" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B210" t="s">
         <v>1024</v>
       </c>
-      <c r="B210" t="s">
-        <v>1025</v>
-      </c>
       <c r="C210" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D210">
         <v>1</v>
@@ -9621,21 +9621,21 @@
       </c>
       <c r="F210" s="6"/>
       <c r="G210" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H210" t="s">
         <v>1026</v>
-      </c>
-      <c r="H210" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B211" t="s">
         <v>1028</v>
       </c>
-      <c r="B211" t="s">
-        <v>1029</v>
-      </c>
       <c r="C211" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -9645,18 +9645,18 @@
       </c>
       <c r="F211" s="6"/>
       <c r="G211" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H211" t="s">
         <v>1030</v>
-      </c>
-      <c r="H211" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B212" t="s">
         <v>1032</v>
-      </c>
-      <c r="B212" t="s">
-        <v>1033</v>
       </c>
       <c r="C212" t="s">
         <v>17</v>
@@ -9669,21 +9669,21 @@
       </c>
       <c r="F212" s="6"/>
       <c r="G212" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H212" t="s">
         <v>1034</v>
-      </c>
-      <c r="H212" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B213" t="s">
         <v>1036</v>
       </c>
-      <c r="B213" t="s">
+      <c r="C213" t="s">
         <v>1037</v>
-      </c>
-      <c r="C213" t="s">
-        <v>1038</v>
       </c>
       <c r="D213">
         <v>1</v>
@@ -9693,21 +9693,21 @@
       </c>
       <c r="F213" s="6"/>
       <c r="G213" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H213" t="s">
         <v>1039</v>
-      </c>
-      <c r="H213" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B214" t="s">
         <v>1041</v>
       </c>
-      <c r="B214" t="s">
+      <c r="C214" t="s">
         <v>1042</v>
-      </c>
-      <c r="C214" t="s">
-        <v>1043</v>
       </c>
       <c r="D214">
         <v>1</v>
@@ -9717,21 +9717,21 @@
       </c>
       <c r="F214" s="6"/>
       <c r="G214" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H214" t="s">
         <v>1044</v>
-      </c>
-      <c r="H214" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B215" t="s">
         <v>1046</v>
       </c>
-      <c r="B215" t="s">
-        <v>1047</v>
-      </c>
       <c r="C215" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D215">
         <v>1</v>
@@ -9741,21 +9741,21 @@
       </c>
       <c r="F215" s="6"/>
       <c r="G215" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H215" t="s">
         <v>1048</v>
-      </c>
-      <c r="H215" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B216" t="s">
         <v>1050</v>
       </c>
-      <c r="B216" t="s">
-        <v>1051</v>
-      </c>
       <c r="C216" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D216">
         <v>1</v>
@@ -9765,21 +9765,21 @@
       </c>
       <c r="F216" s="6"/>
       <c r="G216" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H216" t="s">
         <v>1052</v>
-      </c>
-      <c r="H216" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B217" t="s">
         <v>1054</v>
       </c>
-      <c r="B217" t="s">
+      <c r="C217" t="s">
         <v>1055</v>
-      </c>
-      <c r="C217" t="s">
-        <v>1056</v>
       </c>
       <c r="D217">
         <v>1</v>
@@ -9789,18 +9789,18 @@
       </c>
       <c r="F217" s="6"/>
       <c r="G217" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H217" t="s">
         <v>1057</v>
-      </c>
-      <c r="H217" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B218" t="s">
         <v>1059</v>
-      </c>
-      <c r="B218" t="s">
-        <v>1060</v>
       </c>
       <c r="C218" t="s">
         <v>17</v>
@@ -9813,18 +9813,18 @@
       </c>
       <c r="F218" s="6"/>
       <c r="G218" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H218" t="s">
         <v>1061</v>
-      </c>
-      <c r="H218" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B219" t="s">
         <v>1063</v>
-      </c>
-      <c r="B219" t="s">
-        <v>1064</v>
       </c>
       <c r="C219" t="s">
         <v>17</v>
@@ -9837,18 +9837,18 @@
       </c>
       <c r="F219" s="6"/>
       <c r="G219" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H219" t="s">
         <v>1065</v>
-      </c>
-      <c r="H219" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="220" spans="1:8">
       <c r="A220" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B220" t="s">
         <v>1067</v>
-      </c>
-      <c r="B220" t="s">
-        <v>1068</v>
       </c>
       <c r="C220" t="s">
         <v>17</v>
@@ -9861,18 +9861,18 @@
       </c>
       <c r="F220" s="6"/>
       <c r="G220" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H220" t="s">
         <v>1069</v>
-      </c>
-      <c r="H220" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="221" spans="1:8">
       <c r="A221" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B221" t="s">
         <v>1071</v>
-      </c>
-      <c r="B221" t="s">
-        <v>1072</v>
       </c>
       <c r="C221" t="s">
         <v>58</v>
@@ -9885,18 +9885,18 @@
       </c>
       <c r="F221" s="6"/>
       <c r="G221" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H221" t="s">
         <v>1073</v>
-      </c>
-      <c r="H221" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="222" spans="1:8">
       <c r="A222" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B222" t="s">
         <v>1075</v>
-      </c>
-      <c r="B222" t="s">
-        <v>1076</v>
       </c>
       <c r="C222" t="s">
         <v>58</v>
@@ -9911,13 +9911,13 @@
     </row>
     <row r="223" spans="1:8">
       <c r="A223" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B223" t="s">
         <v>1077</v>
       </c>
-      <c r="B223" t="s">
+      <c r="C223" t="s">
         <v>1078</v>
-      </c>
-      <c r="C223" t="s">
-        <v>1079</v>
       </c>
       <c r="D223">
         <v>1</v>
@@ -9927,21 +9927,21 @@
       </c>
       <c r="F223" s="6"/>
       <c r="G223" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H223" t="s">
         <v>1080</v>
-      </c>
-      <c r="H223" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="224" spans="1:8">
       <c r="A224" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B224" t="s">
         <v>1082</v>
       </c>
-      <c r="B224" t="s">
-        <v>1083</v>
-      </c>
       <c r="C224" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D224">
         <v>1</v>
@@ -9951,21 +9951,21 @@
       </c>
       <c r="F224" s="6"/>
       <c r="G224" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H224" t="s">
         <v>1084</v>
-      </c>
-      <c r="H224" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="225" spans="1:8">
       <c r="A225" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B225" t="s">
         <v>1086</v>
       </c>
-      <c r="B225" t="s">
-        <v>1087</v>
-      </c>
       <c r="C225" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D225">
         <v>1</v>
@@ -9975,18 +9975,18 @@
       </c>
       <c r="F225" s="6"/>
       <c r="G225" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H225" t="s">
         <v>1088</v>
-      </c>
-      <c r="H225" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="226" spans="1:8">
       <c r="A226" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B226" t="s">
         <v>1090</v>
-      </c>
-      <c r="B226" t="s">
-        <v>1091</v>
       </c>
       <c r="C226" t="s">
         <v>58</v>
@@ -10001,13 +10001,13 @@
     </row>
     <row r="227" spans="1:8">
       <c r="A227" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B227" t="s">
         <v>1092</v>
       </c>
-      <c r="B227" t="s">
+      <c r="C227" t="s">
         <v>1093</v>
-      </c>
-      <c r="C227" t="s">
-        <v>1094</v>
       </c>
       <c r="D227">
         <v>1</v>
@@ -10017,21 +10017,21 @@
       </c>
       <c r="F227" s="6"/>
       <c r="G227" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H227" t="s">
         <v>1095</v>
-      </c>
-      <c r="H227" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="228" spans="1:8">
       <c r="A228" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B228" t="s">
         <v>1097</v>
       </c>
-      <c r="B228" t="s">
-        <v>1098</v>
-      </c>
       <c r="C228" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D228">
         <v>1</v>
@@ -10041,21 +10041,21 @@
       </c>
       <c r="F228" s="6"/>
       <c r="G228" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H228" t="s">
         <v>1099</v>
-      </c>
-      <c r="H228" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="229" spans="1:8">
       <c r="A229" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B229" t="s">
         <v>1101</v>
       </c>
-      <c r="B229" t="s">
+      <c r="C229" t="s">
         <v>1102</v>
-      </c>
-      <c r="C229" t="s">
-        <v>1103</v>
       </c>
       <c r="D229">
         <v>1</v>
@@ -10065,18 +10065,18 @@
       </c>
       <c r="F229" s="6"/>
       <c r="G229" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H229" t="s">
         <v>1104</v>
-      </c>
-      <c r="H229" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="230" spans="1:8">
       <c r="A230" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B230" t="s">
         <v>1106</v>
-      </c>
-      <c r="B230" t="s">
-        <v>1107</v>
       </c>
       <c r="C230" t="s">
         <v>58</v>
@@ -10089,18 +10089,18 @@
       </c>
       <c r="F230" s="6"/>
       <c r="G230" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H230" t="s">
         <v>1108</v>
-      </c>
-      <c r="H230" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="231" spans="1:8">
       <c r="A231" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B231" t="s">
         <v>1110</v>
-      </c>
-      <c r="B231" t="s">
-        <v>1111</v>
       </c>
       <c r="C231" t="s">
         <v>58</v>
@@ -10113,21 +10113,21 @@
       </c>
       <c r="F231" s="6"/>
       <c r="G231" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H231" t="s">
         <v>1112</v>
-      </c>
-      <c r="H231" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="232" spans="1:8">
       <c r="A232" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B232" t="s">
         <v>1114</v>
       </c>
-      <c r="B232" t="s">
+      <c r="C232" t="s">
         <v>1115</v>
-      </c>
-      <c r="C232" t="s">
-        <v>1116</v>
       </c>
       <c r="D232">
         <v>1</v>
@@ -10137,21 +10137,21 @@
       </c>
       <c r="F232" s="6"/>
       <c r="G232" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H232" t="s">
         <v>1117</v>
-      </c>
-      <c r="H232" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="233" spans="1:8">
       <c r="A233" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B233" t="s">
         <v>1119</v>
       </c>
-      <c r="B233" t="s">
+      <c r="C233" t="s">
         <v>1120</v>
-      </c>
-      <c r="C233" t="s">
-        <v>1121</v>
       </c>
       <c r="D233">
         <v>1</v>
@@ -10161,21 +10161,21 @@
       </c>
       <c r="F233" s="6"/>
       <c r="G233" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H233" t="s">
         <v>1122</v>
-      </c>
-      <c r="H233" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="234" spans="1:8">
       <c r="A234" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B234" t="s">
         <v>1124</v>
       </c>
-      <c r="B234" t="s">
+      <c r="C234" t="s">
         <v>1125</v>
-      </c>
-      <c r="C234" t="s">
-        <v>1126</v>
       </c>
       <c r="D234">
         <v>1</v>
@@ -10185,18 +10185,18 @@
       </c>
       <c r="F234" s="6"/>
       <c r="G234" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H234" t="s">
         <v>1127</v>
-      </c>
-      <c r="H234" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B235" t="s">
         <v>1129</v>
-      </c>
-      <c r="B235" t="s">
-        <v>1130</v>
       </c>
       <c r="C235" t="s">
         <v>58</v>
@@ -10209,21 +10209,21 @@
       </c>
       <c r="F235" s="6"/>
       <c r="G235" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H235" t="s">
         <v>1131</v>
-      </c>
-      <c r="H235" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B236" t="s">
         <v>1133</v>
       </c>
-      <c r="B236" t="s">
+      <c r="C236" t="s">
         <v>1134</v>
-      </c>
-      <c r="C236" t="s">
-        <v>1135</v>
       </c>
       <c r="D236">
         <v>1</v>
@@ -10233,21 +10233,21 @@
       </c>
       <c r="F236" s="6"/>
       <c r="G236" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H236" t="s">
         <v>1136</v>
-      </c>
-      <c r="H236" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="237" spans="1:8">
       <c r="A237" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B237" t="s">
         <v>1138</v>
       </c>
-      <c r="B237" t="s">
-        <v>1139</v>
-      </c>
       <c r="C237" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D237">
         <v>1</v>
@@ -10257,21 +10257,21 @@
       </c>
       <c r="F237" s="6"/>
       <c r="G237" t="s">
+        <v>1139</v>
+      </c>
+      <c r="H237" t="s">
         <v>1140</v>
-      </c>
-      <c r="H237" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="238" spans="1:8">
       <c r="A238" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B238" t="s">
         <v>1142</v>
       </c>
-      <c r="B238" t="s">
-        <v>1143</v>
-      </c>
       <c r="C238" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D238">
         <v>1</v>
@@ -10281,21 +10281,21 @@
       </c>
       <c r="F238" s="6"/>
       <c r="G238" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H238" t="s">
         <v>1144</v>
-      </c>
-      <c r="H238" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="239" spans="1:8">
       <c r="A239" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B239" t="s">
         <v>1146</v>
       </c>
-      <c r="B239" t="s">
-        <v>1147</v>
-      </c>
       <c r="C239" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D239">
         <v>1</v>
@@ -10305,18 +10305,18 @@
       </c>
       <c r="F239" s="6"/>
       <c r="G239" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H239" t="s">
         <v>1148</v>
-      </c>
-      <c r="H239" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B240" t="s">
         <v>1150</v>
-      </c>
-      <c r="B240" t="s">
-        <v>1151</v>
       </c>
       <c r="C240" t="s">
         <v>58</v>
@@ -10331,10 +10331,10 @@
     </row>
     <row r="241" spans="1:8">
       <c r="A241" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B241" t="s">
         <v>1152</v>
-      </c>
-      <c r="B241" t="s">
-        <v>1153</v>
       </c>
       <c r="C241" t="s">
         <v>58</v>
@@ -10347,21 +10347,21 @@
       </c>
       <c r="F241" s="6"/>
       <c r="G241" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H241" t="s">
         <v>1154</v>
-      </c>
-      <c r="H241" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B242" t="s">
         <v>1156</v>
       </c>
-      <c r="B242" t="s">
+      <c r="C242" t="s">
         <v>1157</v>
-      </c>
-      <c r="C242" t="s">
-        <v>1158</v>
       </c>
       <c r="D242">
         <v>1</v>
@@ -10371,21 +10371,21 @@
       </c>
       <c r="F242" s="6"/>
       <c r="G242" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H242" t="s">
         <v>1159</v>
-      </c>
-      <c r="H242" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="243" spans="1:8">
       <c r="A243" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B243" t="s">
         <v>1161</v>
       </c>
-      <c r="B243" t="s">
+      <c r="C243" t="s">
         <v>1162</v>
-      </c>
-      <c r="C243" t="s">
-        <v>1163</v>
       </c>
       <c r="D243">
         <v>1</v>
@@ -10395,10 +10395,10 @@
       </c>
       <c r="F243" s="6"/>
       <c r="G243" t="s">
+        <v>1163</v>
+      </c>
+      <c r="H243" t="s">
         <v>1164</v>
-      </c>
-      <c r="H243" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="244" spans="1:8" s="3" customFormat="1">
@@ -10406,7 +10406,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>17</v>
@@ -10420,13 +10420,13 @@
     </row>
     <row r="245" spans="1:8">
       <c r="A245" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B245" t="s">
         <v>1166</v>
       </c>
-      <c r="B245" t="s">
+      <c r="C245" t="s">
         <v>1167</v>
-      </c>
-      <c r="C245" t="s">
-        <v>1168</v>
       </c>
       <c r="D245">
         <v>1</v>
@@ -10436,18 +10436,18 @@
       </c>
       <c r="F245" s="6"/>
       <c r="G245" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H245" t="s">
         <v>1169</v>
-      </c>
-      <c r="H245" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B246" t="s">
         <v>1171</v>
-      </c>
-      <c r="B246" t="s">
-        <v>1172</v>
       </c>
       <c r="C246" t="s">
         <v>10</v>
@@ -10460,21 +10460,21 @@
       </c>
       <c r="F246" s="6"/>
       <c r="G246" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H246" t="s">
         <v>1173</v>
-      </c>
-      <c r="H246" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B247" t="s">
         <v>1175</v>
       </c>
-      <c r="B247" t="s">
-        <v>1176</v>
-      </c>
       <c r="C247" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D247">
         <v>1</v>
@@ -10484,18 +10484,18 @@
       </c>
       <c r="F247" s="6"/>
       <c r="G247" t="s">
+        <v>1176</v>
+      </c>
+      <c r="H247" t="s">
         <v>1177</v>
-      </c>
-      <c r="H247" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="248" spans="1:8">
       <c r="A248" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B248" t="s">
         <v>1179</v>
-      </c>
-      <c r="B248" t="s">
-        <v>1180</v>
       </c>
       <c r="C248" t="s">
         <v>58</v>
@@ -10508,21 +10508,21 @@
       </c>
       <c r="F248" s="6"/>
       <c r="G248" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H248" t="s">
         <v>1181</v>
-      </c>
-      <c r="H248" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="249" spans="1:8">
       <c r="A249" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B249" t="s">
         <v>1183</v>
       </c>
-      <c r="B249" t="s">
+      <c r="C249" t="s">
         <v>1184</v>
-      </c>
-      <c r="C249" t="s">
-        <v>1185</v>
       </c>
       <c r="D249">
         <v>1</v>
@@ -10532,18 +10532,18 @@
       </c>
       <c r="F249" s="6"/>
       <c r="G249" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H249" t="s">
         <v>1186</v>
-      </c>
-      <c r="H249" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="250" spans="1:8">
       <c r="A250" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B250" t="s">
         <v>1188</v>
-      </c>
-      <c r="B250" t="s">
-        <v>1189</v>
       </c>
       <c r="C250" t="s">
         <v>58</v>
@@ -10558,13 +10558,13 @@
     </row>
     <row r="251" spans="1:8">
       <c r="A251" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B251" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C251" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D251">
         <v>1</v>
@@ -10576,10 +10576,10 @@
     </row>
     <row r="252" spans="1:8">
       <c r="A252" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B252" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C252" t="s">
         <v>10</v>
@@ -10591,24 +10591,24 @@
         <v>11</v>
       </c>
       <c r="F252" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G252" t="s">
         <v>1192</v>
       </c>
-      <c r="G252" t="s">
+      <c r="H252" t="s">
         <v>1193</v>
-      </c>
-      <c r="H252" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="253" spans="1:8">
       <c r="A253" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B253" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C253" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -10618,18 +10618,18 @@
       </c>
       <c r="F253" s="6"/>
       <c r="G253" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H253" t="s">
         <v>1196</v>
-      </c>
-      <c r="H253" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="254" spans="1:8">
       <c r="A254" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B254" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C254" t="s">
         <v>17</v>
@@ -10642,18 +10642,18 @@
       </c>
       <c r="F254" s="6"/>
       <c r="G254" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H254" t="s">
         <v>1199</v>
-      </c>
-      <c r="H254" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="255" spans="1:8">
       <c r="A255" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B255" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C255" t="s">
         <v>10</v>
@@ -10665,21 +10665,21 @@
         <v>11</v>
       </c>
       <c r="F255" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G255" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H255" t="s">
         <v>1202</v>
-      </c>
-      <c r="G255" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H255" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="256" spans="1:8">
       <c r="A256" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B256" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C256" t="s">
         <v>10</v>
@@ -10692,21 +10692,21 @@
       </c>
       <c r="F256" s="6"/>
       <c r="G256" t="s">
+        <v>1204</v>
+      </c>
+      <c r="H256" t="s">
         <v>1205</v>
-      </c>
-      <c r="H256" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="257" spans="1:8">
       <c r="A257" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B257" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C257" t="s">
         <v>1207</v>
-      </c>
-      <c r="C257" t="s">
-        <v>1208</v>
       </c>
       <c r="D257">
         <v>1</v>
@@ -10716,21 +10716,21 @@
       </c>
       <c r="F257" s="6"/>
       <c r="G257" t="s">
+        <v>1208</v>
+      </c>
+      <c r="H257" t="s">
         <v>1209</v>
-      </c>
-      <c r="H257" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="258" spans="1:8">
       <c r="A258" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B258" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="C258" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D258">
         <v>1</v>
@@ -10740,18 +10740,18 @@
       </c>
       <c r="F258" s="6"/>
       <c r="G258" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H258" t="s">
         <v>1212</v>
-      </c>
-      <c r="H258" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="259" spans="1:8">
       <c r="A259" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B259" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="C259" t="s">
         <v>17</v>
@@ -10764,21 +10764,21 @@
       </c>
       <c r="F259" s="6"/>
       <c r="G259" t="s">
+        <v>1214</v>
+      </c>
+      <c r="H259" t="s">
         <v>1215</v>
-      </c>
-      <c r="H259" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="260" spans="1:8">
       <c r="A260" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B260" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C260" t="s">
         <v>1217</v>
-      </c>
-      <c r="C260" t="s">
-        <v>1218</v>
       </c>
       <c r="D260">
         <v>1</v>
@@ -10790,10 +10790,10 @@
     </row>
     <row r="261" spans="1:8">
       <c r="A261" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B261" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C261" t="s">
         <v>58</v>
@@ -10806,21 +10806,21 @@
       </c>
       <c r="F261" s="6"/>
       <c r="G261" t="s">
+        <v>1219</v>
+      </c>
+      <c r="H261" t="s">
         <v>1220</v>
-      </c>
-      <c r="H261" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="A262" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B262" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C262" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D262">
         <v>1</v>
@@ -10830,18 +10830,18 @@
       </c>
       <c r="F262" s="6"/>
       <c r="G262" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H262" t="s">
         <v>1223</v>
-      </c>
-      <c r="H262" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="263" spans="1:8">
       <c r="A263" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B263" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C263" t="s">
         <v>58</v>
@@ -10854,21 +10854,21 @@
       </c>
       <c r="F263" s="6"/>
       <c r="G263" t="s">
+        <v>1225</v>
+      </c>
+      <c r="H263" t="s">
         <v>1226</v>
-      </c>
-      <c r="H263" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="264" spans="1:8">
       <c r="A264" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B264" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C264" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="D264">
         <v>1</v>
@@ -10878,21 +10878,21 @@
       </c>
       <c r="F264" s="6"/>
       <c r="G264" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H264" t="s">
         <v>1229</v>
-      </c>
-      <c r="H264" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="265" spans="1:8">
       <c r="A265" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B265" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="C265" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D265">
         <v>1</v>
@@ -10904,13 +10904,13 @@
     </row>
     <row r="266" spans="1:8">
       <c r="A266" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B266" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C266" t="s">
         <v>1232</v>
-      </c>
-      <c r="C266" t="s">
-        <v>1233</v>
       </c>
       <c r="D266">
         <v>1</v>
@@ -10922,10 +10922,10 @@
     </row>
     <row r="267" spans="1:8">
       <c r="A267" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B267" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="C267" t="s">
         <v>58</v>
@@ -10938,21 +10938,21 @@
       </c>
       <c r="F267" s="6"/>
       <c r="G267" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H267" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B268" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C268" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D268">
         <v>1</v>
@@ -10964,13 +10964,13 @@
     </row>
     <row r="269" spans="1:8">
       <c r="A269" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B269" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C269" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D269">
         <v>1</v>
@@ -10982,13 +10982,13 @@
     </row>
     <row r="270" spans="1:8">
       <c r="A270" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B270" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C270" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D270">
         <v>1</v>
@@ -10998,21 +10998,21 @@
       </c>
       <c r="F270" s="6"/>
       <c r="G270" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H270" t="s">
         <v>1239</v>
-      </c>
-      <c r="H270" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="271" spans="1:8">
       <c r="A271" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B271" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C271" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D271">
         <v>1</v>
@@ -11022,47 +11022,47 @@
       </c>
       <c r="F271" s="6"/>
       <c r="G271" t="s">
+        <v>1241</v>
+      </c>
+      <c r="H271" t="s">
         <v>1242</v>
-      </c>
-      <c r="H271" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="272" spans="1:8">
       <c r="A272" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B272" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C272" t="s">
         <v>1244</v>
       </c>
-      <c r="C272" t="s">
+      <c r="D272">
+        <v>1</v>
+      </c>
+      <c r="E272" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F272" t="s">
         <v>1245</v>
       </c>
-      <c r="D272">
-        <v>1</v>
-      </c>
-      <c r="E272" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F272" t="s">
+      <c r="G272" t="s">
         <v>1246</v>
       </c>
-      <c r="G272" t="s">
+      <c r="H272" t="s">
         <v>1247</v>
-      </c>
-      <c r="H272" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="273" spans="1:8">
       <c r="A273" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B273" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C273" t="s">
         <v>1249</v>
-      </c>
-      <c r="C273" t="s">
-        <v>1250</v>
       </c>
       <c r="D273">
         <v>1</v>
@@ -11072,21 +11072,21 @@
       </c>
       <c r="F273" s="6"/>
       <c r="G273" t="s">
+        <v>1250</v>
+      </c>
+      <c r="H273" t="s">
         <v>1251</v>
-      </c>
-      <c r="H273" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="274" spans="1:8">
       <c r="A274" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B274" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C274" t="s">
         <v>1253</v>
-      </c>
-      <c r="C274" t="s">
-        <v>1254</v>
       </c>
       <c r="D274">
         <v>16</v>
@@ -11096,21 +11096,21 @@
       </c>
       <c r="F274" s="6"/>
       <c r="G274" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H274" t="s">
         <v>1255</v>
-      </c>
-      <c r="H274" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="275" spans="1:8">
       <c r="A275" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B275" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C275" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D275">
         <v>1</v>
@@ -11121,13 +11121,13 @@
     </row>
     <row r="276" spans="1:8">
       <c r="A276" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B276" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C276" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D276">
         <v>1</v>
@@ -11137,21 +11137,21 @@
       </c>
       <c r="F276" s="6"/>
       <c r="G276" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H276" t="s">
         <v>1259</v>
-      </c>
-      <c r="H276" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="277" spans="1:8">
       <c r="A277" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B277" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C277" t="s">
         <v>1261</v>
-      </c>
-      <c r="C277" t="s">
-        <v>1262</v>
       </c>
       <c r="D277">
         <v>1</v>
@@ -11161,21 +11161,21 @@
       </c>
       <c r="F277" s="6"/>
       <c r="G277" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H277" t="s">
         <v>1263</v>
-      </c>
-      <c r="H277" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="278" spans="1:8">
       <c r="A278" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B278" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C278" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D278">
         <v>1</v>
@@ -11187,13 +11187,13 @@
     </row>
     <row r="279" spans="1:8">
       <c r="A279" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B279" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C279" t="s">
         <v>1266</v>
-      </c>
-      <c r="C279" t="s">
-        <v>1267</v>
       </c>
       <c r="D279">
         <v>1</v>
@@ -11205,10 +11205,10 @@
     </row>
     <row r="280" spans="1:8">
       <c r="A280" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B280" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C280" t="s">
         <v>58</v>
@@ -11221,18 +11221,18 @@
       </c>
       <c r="F280" s="6"/>
       <c r="G280" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H280" t="s">
         <v>1269</v>
-      </c>
-      <c r="H280" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="281" spans="1:8">
       <c r="A281" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B281" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C281" t="s">
         <v>58</v>
@@ -11245,21 +11245,21 @@
       </c>
       <c r="F281" s="6"/>
       <c r="G281" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H281" t="s">
         <v>1272</v>
-      </c>
-      <c r="H281" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B282" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C282" t="s">
         <v>1274</v>
-      </c>
-      <c r="C282" t="s">
-        <v>1275</v>
       </c>
       <c r="D282">
         <v>1</v>
@@ -11269,21 +11269,21 @@
       </c>
       <c r="F282" s="6"/>
       <c r="G282" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H282" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="283" spans="1:8">
       <c r="A283" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B283" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C283" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D283">
         <v>1</v>
@@ -11293,10 +11293,10 @@
       </c>
       <c r="F283" s="6"/>
       <c r="G283" t="s">
+        <v>1277</v>
+      </c>
+      <c r="H283" t="s">
         <v>1278</v>
-      </c>
-      <c r="H283" t="s">
-        <v>1279</v>
       </c>
     </row>
   </sheetData>
